--- a/recomendador_sabaneta/data/base_actualizada.xlsx
+++ b/recomendador_sabaneta/data/base_actualizada.xlsx
@@ -1,50 +1,68 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24334"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Soportedrai\Documents\CarolinaOspina\recomendador_sabaneta\data\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5D8D35F8-B0E3-48D8-B4B3-8C566E60C19C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <bookViews>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+  </bookViews>
   <sheets>
-    <sheet state="visible" name="Temas" sheetId="1" r:id="rId4"/>
-    <sheet state="visible" name="BBDD" sheetId="2" r:id="rId5"/>
-    <sheet state="visible" name="Hoja3" sheetId="3" r:id="rId6"/>
+    <sheet name="Temas" sheetId="1" r:id="rId1"/>
+    <sheet name="BBDD" sheetId="2" r:id="rId2"/>
+    <sheet name="Hoja3" sheetId="3" r:id="rId3"/>
   </sheets>
-  <definedNames/>
-  <calcPr/>
+  <calcPr calcId="191029"/>
   <extLst>
-    <ext uri="GoogleSheetsCustomDataVersion2">
-      <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" r:id="rId7" roundtripDataChecksum="5OXPpGL1HHUsTYc6UpQqTkLXDUb0VZksCaUl3A8MoMs="/>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+      </xcalcf:calcFeatures>
     </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision">
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
   <authors>
-    <author/>
+    <author>None</author>
   </authors>
   <commentList>
-    <comment authorId="0" ref="F1">
+    <comment ref="E1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0100-000001000000}">
       <text>
-        <t xml:space="preserve">======
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color theme="1"/>
+            <rFont val="Aptos Narrow"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t>======
 ID#AAABkz0JtyQ
 tc={5E4AAE11-FFBD-41C2-95C3-FC3F2AF79E96}    (2025-06-20 01:07:08)
 [Comentario encadenado]
 Su versión de Excel le permite leer este comentario encadenado; sin embargo, las ediciones que se apliquen se quitarán si el archivo se abre en una versión más reciente de Excel. Más información: https://go.microsoft.com/fwlink/?linkid=870924
 Comentario:
     Max 10</t>
+        </r>
       </text>
     </comment>
   </commentList>
-  <extLst>
-    <ext uri="GoogleSheetsCustomDataVersion2">
-      <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" r:id="rId1" roundtripDataSignature="AMtx7mikP1qmZYmSN8mHAcf1jET8Cul9ag=="/>
-    </ext>
-  </extLst>
 </comments>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="718" uniqueCount="250">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="758" uniqueCount="254">
   <si>
     <t>Introducción teorica sobre el ciclo de vida de proyecto de ML</t>
   </si>
@@ -73,9 +91,6 @@
     <t>Desarrollo</t>
   </si>
   <si>
-    <t>ID</t>
-  </si>
-  <si>
     <t>NIT</t>
   </si>
   <si>
@@ -115,16 +130,16 @@
     <t>LINK_INSTAGRAM</t>
   </si>
   <si>
-    <t>FERRETERIA ABC</t>
-  </si>
-  <si>
-    <t>FERRETERO</t>
-  </si>
-  <si>
-    <t>FERRETERIA</t>
-  </si>
-  <si>
-    <t>TORNILLO, PINTURA, TUBERIA, LAMPARA, BROCHA</t>
+    <t>Casa Musical Vivaldi</t>
+  </si>
+  <si>
+    <t>ELECTRONICO</t>
+  </si>
+  <si>
+    <t>ELECTRODOMESTICOS</t>
+  </si>
+  <si>
+    <t>EQUIPOS DE SONIDO, VIDEO</t>
   </si>
   <si>
     <t>COLOMBIA</t>
@@ -136,43 +151,13 @@
     <t>SABANETA</t>
   </si>
   <si>
-    <t>CRA BLA #BLA-BLA</t>
-  </si>
-  <si>
-    <t>0642564861</t>
-  </si>
-  <si>
-    <t>FACEBOOK/FERRERIA</t>
-  </si>
-  <si>
-    <t>BAL</t>
-  </si>
-  <si>
-    <t>Casa Musical Vivaldi</t>
-  </si>
-  <si>
-    <t>ELECTRONICO</t>
-  </si>
-  <si>
-    <t>ELECTRODOMESTICOS</t>
-  </si>
-  <si>
-    <t>EQUIPOS DE SONIDO, VIDEO</t>
-  </si>
-  <si>
     <t>Carrera 48 #50 sur 128 Local 9913</t>
   </si>
   <si>
     <t>NULL</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <color rgb="FF1155CC"/>
-        <u/>
-      </rPr>
-      <t>Musical Vivaldi Mayorca | Sabaneta | Facebook</t>
-    </r>
+    <t>Musical Vivaldi Mayorca | Sabaneta | Facebook</t>
   </si>
   <si>
     <t>Guillego</t>
@@ -187,22 +172,10 @@
     <t>Cl. 78 Sur #46 B 78</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <color rgb="FF1155CC"/>
-        <u/>
-      </rPr>
-      <t>Magenta Studio | Facebook</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <color rgb="FF1155CC"/>
-        <u/>
-      </rPr>
-      <t>MAGENTA STUDIO (@magentastudiosab) • Fotos y videos de Instagram</t>
-    </r>
+    <t>Magenta Studio | Facebook</t>
+  </si>
+  <si>
+    <t>MAGENTA STUDIO (@magentastudiosab) • Fotos y videos de Instagram</t>
   </si>
   <si>
     <t>Soporte Tv Sabaneta</t>
@@ -214,7 +187,7 @@
     <t>Foto Vasco</t>
   </si>
   <si>
-    <t>Cra. 45</t>
+    <t>NO APLICA</t>
   </si>
   <si>
     <t>Electro Berna</t>
@@ -247,9 +220,6 @@
     <t>Ordenadores, equipo periferico, electrodomestico, telecomunicaciones</t>
   </si>
   <si>
-    <t>Cl. 62 Sur</t>
-  </si>
-  <si>
     <t>Grupo Hinode</t>
   </si>
   <si>
@@ -304,7 +274,7 @@
     <t xml:space="preserve">Cruz Verde domicilios </t>
   </si>
   <si>
-    <t>Parque Sabaneta, Cra. 43C #68A sur 02</t>
+    <t>Cra. 43C #68A sur 02</t>
   </si>
   <si>
     <t>www.cruzverde.com.co</t>
@@ -478,7 +448,7 @@
     <t>ServiFarma</t>
   </si>
   <si>
-    <t>Cra. 47 #75 Sur-128 a 75 Sur-2</t>
+    <t>Cra. 47 #75 Sur-128</t>
   </si>
   <si>
     <t>3222186</t>
@@ -487,7 +457,7 @@
     <t>Droguería San Joaquín</t>
   </si>
   <si>
-    <t>Cl. 69 Sur #43C-06, Santa Ana</t>
+    <t>Cl. 69 Sur #43C-06</t>
   </si>
   <si>
     <t>Botica Junín</t>
@@ -511,7 +481,7 @@
     <t>Redihos S.A.S</t>
   </si>
   <si>
-    <t>Cra. 49 #61 sur 540 Bg 133</t>
+    <t>Cra. 49 #61 sur 540</t>
   </si>
   <si>
     <t>www.redihos.com.co</t>
@@ -553,7 +523,7 @@
     <t>Medicamentos, Implementos de aseo personal, facial, corporal</t>
   </si>
   <si>
-    <t>Cl. 75 Sur #47-38, Calle Larga</t>
+    <t>Cl. 75 Sur #47-38</t>
   </si>
   <si>
     <t>https://www.facebook.com/DrogueriaLuzDelDia/</t>
@@ -571,7 +541,7 @@
     <t>Drogueria Colsubsidio Aves Maria</t>
   </si>
   <si>
-    <t>Cl. 75 Sur #43a - 202 Local 236</t>
+    <t>Cl. 75 Sur #43a - 202</t>
   </si>
   <si>
     <t>Drogueria Flash Market</t>
@@ -583,7 +553,7 @@
     <t>Droguería Colsubsidio Centro Comercial Mayorca</t>
   </si>
   <si>
-    <t>Carrera 48 No 50 Sur - 128 Piso 3 Local 3013 C.C. Mayorca</t>
+    <t>Carrera 48 No 50 Sur - 128</t>
   </si>
   <si>
     <t>www.drogueriascolsubsidio.com</t>
@@ -607,7 +577,7 @@
     <t>Roll con palmito de cangrejo, Camarones apanados, Queso Crema, Toping de palmito cryspi</t>
   </si>
   <si>
-    <t>Cl. 76 Sur #46 - 81, Sabaneta, Antioquia, Colombia</t>
+    <t>Cl. 76 Sur #46 - 81</t>
   </si>
   <si>
     <t>320 2847577</t>
@@ -622,7 +592,7 @@
     <t>Niguiri de Massago, Lomo Saltado, Ceviches de Algas, Sopa Ramen</t>
   </si>
   <si>
-    <t>Cl. 70 Sur # 43a-57, Sabaneta, Antioquia, Colombia</t>
+    <t>Cl. 70 Sur # 43a-57</t>
   </si>
   <si>
     <t>318 5444714</t>
@@ -637,7 +607,7 @@
     <t>Sushi Burrito, Platos Teriyaki, bentos, ramen</t>
   </si>
   <si>
-    <t>C.C. Mayorca Etapa III, Cra. 48 #50Sur-128, Local 2077, Sabaneta, Antioquia, Colombia</t>
+    <t>Cra. 48 #50Sur-128</t>
   </si>
   <si>
     <t>344 441100</t>
@@ -649,7 +619,7 @@
     <t>Sushi To Go Vegas</t>
   </si>
   <si>
-    <t>Suchi</t>
+    <t>Suchi, canción</t>
   </si>
   <si>
     <t>Cr48 25 AA S-70</t>
@@ -664,7 +634,7 @@
     <t>Sachimi mixto, entrada esferas del dragon, Niguiri</t>
   </si>
   <si>
-    <t>Calle 72 Sur#43b-29 Sabaneta Colombia</t>
+    <t>Calle 72 Sur#43b-29</t>
   </si>
   <si>
     <t>304 5654626</t>
@@ -694,9 +664,6 @@
     <t>Perros, perras, hamburguesas</t>
   </si>
   <si>
-    <t xml:space="preserve">75 B Sur, Cra. 45 #118 </t>
-  </si>
-  <si>
     <t>https://www.google.com/maps/?cid=6046564733099870232</t>
   </si>
   <si>
@@ -760,7 +727,7 @@
     <t>Bonanza Parrilla</t>
   </si>
   <si>
-    <t xml:space="preserve">Cra. 48 #50 Sur-96 a 50 Sur-272 </t>
+    <t>Cra. 48 #50 Sur-96</t>
   </si>
   <si>
     <t>https://www.google.com/maps/?cid=15207518324423940733</t>
@@ -769,9 +736,6 @@
     <t>Pomodorino</t>
   </si>
   <si>
-    <t xml:space="preserve">Calle 72 sur, Cra. 43A #25 </t>
-  </si>
-  <si>
     <t>https://www.facebook.com/821706404622007/</t>
   </si>
   <si>
@@ -799,6 +763,48 @@
     <t>mrchipsgourmet.negocio.site</t>
   </si>
   <si>
+    <t>Organika esencial</t>
+  </si>
+  <si>
+    <t>COSMETOLOGIA NATURAL</t>
+  </si>
+  <si>
+    <t>humectante</t>
+  </si>
+  <si>
+    <t>Colombia</t>
+  </si>
+  <si>
+    <t>Antioquia</t>
+  </si>
+  <si>
+    <t>Sabaneta</t>
+  </si>
+  <si>
+    <t>3113109548</t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/organika_esencial</t>
+  </si>
+  <si>
+    <t>Organika esencial2</t>
+  </si>
+  <si>
+    <t>exfoliante, syndet</t>
+  </si>
+  <si>
+    <t>nanana</t>
+  </si>
+  <si>
+    <t>nananana</t>
+  </si>
+  <si>
+    <t>nanaanan</t>
+  </si>
+  <si>
+    <t>N/A</t>
+  </si>
+  <si>
     <t>MV</t>
   </si>
   <si>
@@ -812,64 +818,73 @@
   </si>
   <si>
     <t>Calificación de los locales</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Calle 75 B Sur # 45-118 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Calle 72 sur # 43A-25 </t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <fonts count="11">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="10">
     <font>
-      <sz val="11.0"/>
+      <sz val="11"/>
       <color theme="1"/>
       <name val="Aptos Narrow"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="11"/>
       <color theme="1"/>
       <name val="Aptos Narrow"/>
       <scheme val="minor"/>
     </font>
     <font>
       <b/>
-      <sz val="11.0"/>
+      <sz val="11"/>
       <color theme="1"/>
       <name val="Aptos Narrow"/>
     </font>
     <font>
+      <sz val="11"/>
       <color theme="1"/>
       <name val="Arial"/>
     </font>
     <font>
-      <sz val="11.0"/>
-      <color theme="1"/>
-      <name val="Aptos Narrow"/>
-    </font>
-    <font>
-      <sz val="11.0"/>
+      <sz val="11"/>
       <color rgb="FF000000"/>
       <name val="Arial"/>
     </font>
     <font>
       <u/>
+      <sz val="11"/>
       <color rgb="FF0000FF"/>
+      <name val="Aptos Narrow"/>
     </font>
     <font>
       <u/>
+      <sz val="11"/>
       <color rgb="FF0000FF"/>
       <name val="Arial"/>
     </font>
     <font>
       <u/>
+      <sz val="11"/>
       <color rgb="FF467886"/>
       <name val="Arial"/>
     </font>
     <font>
+      <sz val="11"/>
       <color rgb="FF000000"/>
       <name val="Arial"/>
     </font>
     <font>
       <u/>
+      <sz val="11"/>
       <color rgb="FF0000FF"/>
       <name val="Arial"/>
     </font>
@@ -879,7 +894,7 @@
       <patternFill patternType="none"/>
     </fill>
     <fill>
-      <patternFill patternType="lightGray"/>
+      <patternFill patternType="gray125"/>
     </fill>
     <fill>
       <patternFill patternType="solid">
@@ -889,100 +904,67 @@
     </fill>
   </fills>
   <borders count="1">
-    <border/>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="24">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
+  <cellXfs count="16">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyFont="1"/>
-    <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyFont="1"/>
-    <xf borderId="0" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" wrapText="1"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="4" numFmtId="1" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="4" numFmtId="49" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0" vertical="center"/>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
     </xf>
-    <xf borderId="0" fillId="2" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
-      <alignment readingOrder="0" vertical="center"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0"/>
-    </xf>
-    <xf borderId="0" fillId="2" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0" vertical="center"/>
-    </xf>
-    <xf borderId="0" fillId="2" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment shrinkToFit="0" wrapText="1"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyFont="1"/>
-    <xf borderId="0" fillId="0" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="8" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="9" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment horizontal="left" readingOrder="0"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="10" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0"/>
-    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle xfId="0" name="Normal" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
-<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
-</file>
-
-<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
-</file>
-
-<file path=xl/drawings/drawing3.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
-</file>
-
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheets">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Sheets">
   <a:themeElements>
     <a:clrScheme name="Sheets">
       <a:dk1>
@@ -1172,26 +1154,26 @@
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
+  <a:objectDefaults/>
+  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-  <sheetPr>
-    <pageSetUpPr/>
-  </sheetPr>
-  <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.0"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="B1:D1000"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="12.59765625" defaultRowHeight="15" customHeight="1"/>
   <cols>
-    <col customWidth="1" min="1" max="1" width="4.13"/>
-    <col customWidth="1" min="2" max="2" width="1.88"/>
-    <col customWidth="1" min="3" max="3" width="49.63"/>
-    <col customWidth="1" min="4" max="26" width="10.63"/>
+    <col min="1" max="1" width="4.09765625" customWidth="1"/>
+    <col min="2" max="2" width="1.8984375" customWidth="1"/>
+    <col min="3" max="3" width="49.59765625" customWidth="1"/>
+    <col min="4" max="26" width="10.59765625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="14.25" customHeight="1"/>
-    <row r="2" ht="14.25" customHeight="1">
+    <row r="1" spans="2:4" ht="14.25" customHeight="1"/>
+    <row r="2" spans="2:4" ht="14.25" customHeight="1">
       <c r="B2" s="1">
-        <v>1.0</v>
+        <v>1</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>0</v>
@@ -1200,9 +1182,9 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" ht="14.25" customHeight="1">
+    <row r="3" spans="2:4" ht="14.25" customHeight="1">
       <c r="B3" s="1">
-        <f t="shared" ref="B3:B6" si="1">+B2+1</f>
+        <f>+B2+1</f>
         <v>2</v>
       </c>
       <c r="C3" s="1" t="s">
@@ -1212,9 +1194,9 @@
         <v>3</v>
       </c>
     </row>
-    <row r="4" ht="14.25" customHeight="1">
+    <row r="4" spans="2:4" ht="14.25" customHeight="1">
       <c r="B4" s="1">
-        <f t="shared" si="1"/>
+        <f>+B3+1</f>
         <v>3</v>
       </c>
       <c r="C4" s="1" t="s">
@@ -1224,9 +1206,9 @@
         <v>5</v>
       </c>
     </row>
-    <row r="5" ht="14.25" customHeight="1">
+    <row r="5" spans="2:4" ht="14.25" customHeight="1">
       <c r="B5" s="1">
-        <f t="shared" si="1"/>
+        <f>+B4+1</f>
         <v>4</v>
       </c>
       <c r="C5" s="1" t="s">
@@ -1236,9 +1218,9 @@
         <v>7</v>
       </c>
     </row>
-    <row r="6" ht="14.25" customHeight="1">
+    <row r="6" spans="2:4" ht="14.25" customHeight="1">
       <c r="B6" s="1">
-        <f t="shared" si="1"/>
+        <f>+B5+1</f>
         <v>5</v>
       </c>
       <c r="C6" s="1" t="s">
@@ -1248,16 +1230,16 @@
         <v>5</v>
       </c>
     </row>
-    <row r="7" ht="14.25" customHeight="1"/>
-    <row r="8" ht="14.25" customHeight="1"/>
-    <row r="9" ht="14.25" customHeight="1"/>
-    <row r="10" ht="14.25" customHeight="1"/>
-    <row r="11" ht="14.25" customHeight="1"/>
-    <row r="12" ht="14.25" customHeight="1"/>
-    <row r="13" ht="14.25" customHeight="1"/>
-    <row r="14" ht="14.25" customHeight="1"/>
-    <row r="15" ht="14.25" customHeight="1"/>
-    <row r="16" ht="14.25" customHeight="1"/>
+    <row r="7" spans="2:4" ht="14.25" customHeight="1"/>
+    <row r="8" spans="2:4" ht="14.25" customHeight="1"/>
+    <row r="9" spans="2:4" ht="14.25" customHeight="1"/>
+    <row r="10" spans="2:4" ht="14.25" customHeight="1"/>
+    <row r="11" spans="2:4" ht="14.25" customHeight="1"/>
+    <row r="12" spans="2:4" ht="14.25" customHeight="1"/>
+    <row r="13" spans="2:4" ht="14.25" customHeight="1"/>
+    <row r="14" spans="2:4" ht="14.25" customHeight="1"/>
+    <row r="15" spans="2:4" ht="14.25" customHeight="1"/>
+    <row r="16" spans="2:4" ht="14.25" customHeight="1"/>
     <row r="17" ht="14.25" customHeight="1"/>
     <row r="18" ht="14.25" customHeight="1"/>
     <row r="19" ht="14.25" customHeight="1"/>
@@ -2243,36 +2225,31 @@
     <row r="999" ht="14.25" customHeight="1"/>
     <row r="1000" ht="14.25" customHeight="1"/>
   </sheetData>
-  <printOptions/>
-  <pageMargins bottom="0.75" footer="0.0" header="0.0" left="0.7" right="0.7" top="0.75"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
   <pageSetup orientation="landscape"/>
-  <drawing r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-  <sheetPr>
-    <pageSetUpPr/>
-  </sheetPr>
-  <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.0"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+  <dimension ref="A1:Y993"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="12.59765625" defaultRowHeight="15" customHeight="1"/>
   <cols>
-    <col customWidth="1" min="1" max="1" width="2.88"/>
-    <col customWidth="1" min="2" max="2" width="11.88"/>
-    <col customWidth="1" min="3" max="3" width="26.88"/>
-    <col customWidth="1" min="4" max="4" width="16.25"/>
-    <col customWidth="1" min="5" max="5" width="24.75"/>
-    <col customWidth="1" min="6" max="6" width="25.88"/>
-    <col customWidth="1" min="7" max="7" width="12.0"/>
-    <col customWidth="1" min="8" max="9" width="14.38"/>
-    <col customWidth="1" min="10" max="10" width="50.88"/>
-    <col customWidth="1" min="11" max="11" width="15.5"/>
-    <col customWidth="1" min="12" max="12" width="15.13"/>
-    <col customWidth="1" min="13" max="14" width="64.25"/>
-    <col customWidth="1" min="15" max="26" width="10.63"/>
+    <col min="1" max="1" width="11.8984375" customWidth="1"/>
+    <col min="2" max="2" width="26.8984375" customWidth="1"/>
+    <col min="3" max="3" width="16.296875" customWidth="1"/>
+    <col min="4" max="4" width="24.69921875" customWidth="1"/>
+    <col min="5" max="5" width="48.296875" customWidth="1"/>
+    <col min="6" max="6" width="12" customWidth="1"/>
+    <col min="7" max="8" width="14.3984375" customWidth="1"/>
+    <col min="9" max="9" width="50.8984375" customWidth="1"/>
+    <col min="10" max="10" width="15.3984375" customWidth="1"/>
+    <col min="11" max="11" width="15.09765625" customWidth="1"/>
+    <col min="12" max="13" width="64.296875" customWidth="1"/>
+    <col min="14" max="25" width="10.59765625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="14.25" customHeight="1">
+    <row r="1" spans="1:25" ht="14.25" customHeight="1">
       <c r="A1" s="2" t="s">
         <v>9</v>
       </c>
@@ -2312,9 +2289,7 @@
       <c r="M1" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="N1" s="2" t="s">
-        <v>22</v>
-      </c>
+      <c r="N1" s="2"/>
       <c r="O1" s="2"/>
       <c r="P1" s="2"/>
       <c r="Q1" s="2"/>
@@ -2326,2543 +2301,2465 @@
       <c r="W1" s="2"/>
       <c r="X1" s="2"/>
       <c r="Y1" s="2"/>
-      <c r="Z1" s="2"/>
-    </row>
-    <row r="2" ht="14.25" customHeight="1">
-      <c r="A2" s="1">
-        <v>1.0</v>
-      </c>
-      <c r="B2" s="1">
-        <v>9.0012038855E10</v>
-      </c>
-      <c r="C2" s="1" t="s">
+    </row>
+    <row r="2" spans="1:25" ht="14.25" customHeight="1">
+      <c r="B2" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="C2" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="D2" s="1" t="s">
+      <c r="D2" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="E2" s="1" t="s">
+      <c r="E2" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="F2" s="3" t="s">
+      <c r="F2" s="5" t="s">
         <v>26</v>
       </c>
-      <c r="G2" s="4" t="s">
+      <c r="G2" s="5" t="s">
         <v>27</v>
       </c>
-      <c r="H2" s="4" t="s">
+      <c r="H2" s="5" t="s">
         <v>28</v>
       </c>
-      <c r="I2" s="4" t="s">
+      <c r="I2" s="6" t="s">
         <v>29</v>
       </c>
       <c r="J2" s="5" t="s">
         <v>30</v>
       </c>
-      <c r="K2" s="6">
-        <v>5.73111234567E11</v>
+      <c r="K2" s="5">
+        <v>643662818</v>
       </c>
       <c r="L2" s="7" t="s">
         <v>31</v>
       </c>
       <c r="M2" s="8" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="3" spans="1:25" ht="14.25" customHeight="1">
+      <c r="B3" s="4" t="s">
         <v>32</v>
       </c>
-      <c r="N2" s="8" t="s">
+      <c r="C3" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="D3" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="E3" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="F3" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="G3" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="H3" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="I3" s="6" t="s">
         <v>33</v>
       </c>
-    </row>
-    <row r="3" ht="14.25" customHeight="1">
-      <c r="A3" s="1">
-        <v>2.0</v>
-      </c>
-      <c r="C3" s="9" t="s">
+      <c r="J3" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="K3" s="5">
+        <v>2880992</v>
+      </c>
+      <c r="L3" s="8" t="s">
+        <v>30</v>
+      </c>
+      <c r="M3" s="8" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="4" spans="1:25" ht="14.25" customHeight="1">
+      <c r="B4" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="D3" s="9" t="s">
+      <c r="C4" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="D4" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="E4" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="F4" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="G4" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="H4" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="I4" s="6" t="s">
         <v>35</v>
       </c>
-      <c r="E3" s="9" t="s">
+      <c r="J4" s="5">
+        <v>3128626706</v>
+      </c>
+      <c r="K4" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="L4" s="7" t="s">
         <v>36</v>
       </c>
-      <c r="F3" s="3" t="s">
+      <c r="M4" s="7" t="s">
         <v>37</v>
       </c>
-      <c r="G3" s="10" t="s">
+    </row>
+    <row r="5" spans="1:25" ht="14.25" customHeight="1">
+      <c r="B5" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="C5" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="D5" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="E5" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="F5" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="G5" s="5" t="s">
         <v>27</v>
       </c>
-      <c r="H3" s="10" t="s">
+      <c r="H5" s="5" t="s">
         <v>28</v>
       </c>
-      <c r="I3" s="10" t="s">
-        <v>29</v>
-      </c>
-      <c r="J3" s="11" t="s">
-        <v>38</v>
-      </c>
-      <c r="K3" s="10" t="s">
+      <c r="I5" s="6" t="s">
         <v>39</v>
       </c>
-      <c r="L3" s="10">
-        <v>6.43662818E8</v>
-      </c>
-      <c r="M3" s="12" t="s">
+      <c r="J5" s="5">
+        <v>3152000612</v>
+      </c>
+      <c r="K5" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="L5" s="8" t="s">
+        <v>30</v>
+      </c>
+      <c r="M5" s="8" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="6" spans="1:25" ht="14.25" customHeight="1">
+      <c r="B6" s="4" t="s">
         <v>40</v>
       </c>
-      <c r="N3" s="13" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="4" ht="14.25" customHeight="1">
-      <c r="A4" s="1">
-        <v>3.0</v>
-      </c>
-      <c r="C4" s="9" t="s">
+      <c r="C6" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="D6" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="E6" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="F6" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="G6" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="H6" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="I6" s="6" t="s">
         <v>41</v>
       </c>
-      <c r="D4" s="9" t="s">
-        <v>35</v>
-      </c>
-      <c r="E4" s="9" t="s">
-        <v>36</v>
-      </c>
-      <c r="F4" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="G4" s="10" t="s">
+      <c r="J6" s="5">
+        <v>3005583123</v>
+      </c>
+      <c r="K6" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="L6" s="8" t="s">
+        <v>30</v>
+      </c>
+      <c r="M6" s="8" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="7" spans="1:25" ht="14.25" customHeight="1">
+      <c r="B7" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="C7" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="D7" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="E7" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="F7" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="G7" s="5" t="s">
         <v>27</v>
       </c>
-      <c r="H4" s="10" t="s">
+      <c r="H7" s="5" t="s">
         <v>28</v>
       </c>
-      <c r="I4" s="10" t="s">
-        <v>29</v>
-      </c>
-      <c r="J4" s="11" t="s">
-        <v>42</v>
-      </c>
-      <c r="K4" s="10" t="s">
-        <v>39</v>
-      </c>
-      <c r="L4" s="10">
-        <v>2880992.0</v>
-      </c>
-      <c r="M4" s="13" t="s">
-        <v>39</v>
-      </c>
-      <c r="N4" s="13" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="5" ht="14.25" customHeight="1">
-      <c r="A5" s="1">
-        <v>4.0</v>
-      </c>
-      <c r="C5" s="9" t="s">
+      <c r="I7" s="6" t="s">
         <v>43</v>
       </c>
-      <c r="D5" s="9" t="s">
-        <v>35</v>
-      </c>
-      <c r="E5" s="9" t="s">
-        <v>36</v>
-      </c>
-      <c r="F5" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="G5" s="10" t="s">
+      <c r="J7" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="K7" s="5">
+        <v>6129548</v>
+      </c>
+      <c r="L7" s="8" t="s">
+        <v>30</v>
+      </c>
+      <c r="M7" s="8" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="8" spans="1:25" ht="14.25" customHeight="1">
+      <c r="B8" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="C8" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="D8" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="E8" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="F8" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="G8" s="5" t="s">
         <v>27</v>
       </c>
-      <c r="H5" s="10" t="s">
+      <c r="H8" s="5" t="s">
         <v>28</v>
       </c>
-      <c r="I5" s="10" t="s">
-        <v>29</v>
-      </c>
-      <c r="J5" s="11" t="s">
-        <v>44</v>
-      </c>
-      <c r="K5" s="10">
-        <v>3.128626706E9</v>
-      </c>
-      <c r="L5" s="10" t="s">
-        <v>39</v>
-      </c>
-      <c r="M5" s="12" t="s">
-        <v>45</v>
-      </c>
-      <c r="N5" s="12" t="s">
+      <c r="I8" s="6" t="s">
         <v>46</v>
       </c>
-    </row>
-    <row r="6" ht="14.25" customHeight="1">
-      <c r="A6" s="1">
-        <v>5.0</v>
-      </c>
-      <c r="C6" s="9" t="s">
+      <c r="J8" s="5">
+        <v>3187705846</v>
+      </c>
+      <c r="K8" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="L8" s="8" t="s">
+        <v>30</v>
+      </c>
+      <c r="M8" s="8" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="9" spans="1:25" ht="14.25" customHeight="1">
+      <c r="B9" s="4" t="s">
         <v>47</v>
       </c>
-      <c r="D6" s="9" t="s">
-        <v>35</v>
-      </c>
-      <c r="E6" s="9" t="s">
-        <v>36</v>
-      </c>
-      <c r="F6" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="G6" s="10" t="s">
+      <c r="C9" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="D9" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="E9" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="F9" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="G9" s="5" t="s">
         <v>27</v>
       </c>
-      <c r="H6" s="10" t="s">
+      <c r="H9" s="5" t="s">
         <v>28</v>
       </c>
-      <c r="I6" s="10" t="s">
-        <v>29</v>
-      </c>
-      <c r="J6" s="14" t="s">
-        <v>48</v>
-      </c>
-      <c r="K6" s="10">
-        <v>3.152000612E9</v>
-      </c>
-      <c r="L6" s="10" t="s">
-        <v>39</v>
-      </c>
-      <c r="M6" s="13" t="s">
-        <v>39</v>
-      </c>
-      <c r="N6" s="13" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="7" ht="14.25" customHeight="1">
-      <c r="A7" s="1">
-        <v>6.0</v>
-      </c>
-      <c r="C7" s="9" t="s">
+      <c r="I9" s="6" t="s">
         <v>49</v>
       </c>
-      <c r="D7" s="9" t="s">
-        <v>35</v>
-      </c>
-      <c r="E7" s="9" t="s">
-        <v>36</v>
-      </c>
-      <c r="F7" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="G7" s="10" t="s">
+      <c r="J9" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="K9" s="5">
+        <v>3011751</v>
+      </c>
+      <c r="L9" s="8" t="s">
+        <v>30</v>
+      </c>
+      <c r="M9" s="8" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="10" spans="1:25" ht="14.25" customHeight="1">
+      <c r="B10" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="C10" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="D10" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="E10" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="F10" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="G10" s="5" t="s">
         <v>27</v>
       </c>
-      <c r="H7" s="10" t="s">
+      <c r="H10" s="5" t="s">
         <v>28</v>
       </c>
-      <c r="I7" s="10" t="s">
-        <v>29</v>
-      </c>
-      <c r="J7" s="14" t="s">
-        <v>50</v>
-      </c>
-      <c r="K7" s="10">
-        <v>3.005583123E9</v>
-      </c>
-      <c r="L7" s="10" t="s">
-        <v>39</v>
-      </c>
-      <c r="M7" s="13" t="s">
-        <v>39</v>
-      </c>
-      <c r="N7" s="13" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="8" ht="14.25" customHeight="1">
-      <c r="A8" s="1">
-        <v>7.0</v>
-      </c>
-      <c r="C8" s="9" t="s">
-        <v>51</v>
-      </c>
-      <c r="D8" s="9" t="s">
-        <v>35</v>
-      </c>
-      <c r="E8" s="9" t="s">
-        <v>36</v>
-      </c>
-      <c r="F8" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="G8" s="10" t="s">
+      <c r="I10" s="6" t="s">
+        <v>41</v>
+      </c>
+      <c r="J10" s="5">
+        <v>3103511752</v>
+      </c>
+      <c r="K10" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="L10" s="8" t="s">
+        <v>30</v>
+      </c>
+      <c r="M10" s="8" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="11" spans="1:25" ht="14.25" customHeight="1">
+      <c r="B11" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="C11" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="D11" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="E11" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="F11" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="G11" s="4" t="s">
         <v>27</v>
       </c>
-      <c r="H8" s="10" t="s">
+      <c r="H11" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="I8" s="10" t="s">
-        <v>29</v>
-      </c>
-      <c r="J8" s="14" t="s">
-        <v>52</v>
-      </c>
-      <c r="K8" s="10" t="s">
-        <v>39</v>
-      </c>
-      <c r="L8" s="10">
-        <v>6129548.0</v>
-      </c>
-      <c r="M8" s="13" t="s">
-        <v>39</v>
-      </c>
-      <c r="N8" s="13" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="9" ht="14.25" customHeight="1">
-      <c r="A9" s="1">
-        <v>8.0</v>
-      </c>
-      <c r="C9" s="9" t="s">
-        <v>53</v>
-      </c>
-      <c r="D9" s="9" t="s">
-        <v>35</v>
-      </c>
-      <c r="E9" s="9" t="s">
-        <v>36</v>
-      </c>
-      <c r="F9" s="3" t="s">
+      <c r="I11" s="4" t="s">
         <v>54</v>
       </c>
-      <c r="G9" s="10" t="s">
+      <c r="J11" s="4">
+        <v>3137434048</v>
+      </c>
+      <c r="K11" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="L11" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="M11" s="5" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="12" spans="1:25" ht="14.25" customHeight="1">
+      <c r="B12" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="C12" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="D12" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="E12" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="F12" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="G12" s="4" t="s">
         <v>27</v>
       </c>
-      <c r="H9" s="10" t="s">
+      <c r="H12" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="I9" s="10" t="s">
-        <v>29</v>
-      </c>
-      <c r="J9" s="14" t="s">
-        <v>55</v>
-      </c>
-      <c r="K9" s="10">
-        <v>3.187705846E9</v>
-      </c>
-      <c r="L9" s="10" t="s">
-        <v>39</v>
-      </c>
-      <c r="M9" s="13" t="s">
-        <v>39</v>
-      </c>
-      <c r="N9" s="13" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="10" ht="14.25" customHeight="1">
-      <c r="A10" s="1">
-        <v>9.0</v>
-      </c>
-      <c r="C10" s="9" t="s">
-        <v>56</v>
-      </c>
-      <c r="D10" s="9" t="s">
-        <v>35</v>
-      </c>
-      <c r="E10" s="9" t="s">
-        <v>36</v>
-      </c>
-      <c r="F10" s="3" t="s">
+      <c r="I12" s="9" t="s">
         <v>57</v>
       </c>
-      <c r="G10" s="10" t="s">
+      <c r="J12" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="K12" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="L12" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="M12" s="4" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="13" spans="1:25" ht="14.25" customHeight="1">
+      <c r="B13" s="10" t="s">
+        <v>58</v>
+      </c>
+      <c r="C13" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="D13" s="4" t="s">
+        <v>60</v>
+      </c>
+      <c r="E13" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="F13" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="G13" s="4" t="s">
         <v>27</v>
       </c>
-      <c r="H10" s="10" t="s">
+      <c r="H13" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="I10" s="10" t="s">
-        <v>29</v>
-      </c>
-      <c r="J10" s="14" t="s">
-        <v>58</v>
-      </c>
-      <c r="K10" s="10" t="s">
-        <v>39</v>
-      </c>
-      <c r="L10" s="10">
-        <v>3011751.0</v>
-      </c>
-      <c r="M10" s="13" t="s">
-        <v>39</v>
-      </c>
-      <c r="N10" s="13" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="11" ht="14.25" customHeight="1">
-      <c r="A11" s="1">
-        <v>10.0</v>
-      </c>
-      <c r="C11" s="3" t="s">
+      <c r="I13" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="J13" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="K13" s="4">
+        <v>343224172</v>
+      </c>
+      <c r="L13" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="M13" s="4" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="14" spans="1:25" ht="14.25" customHeight="1">
+      <c r="B14" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="C14" s="4" t="s">
         <v>59</v>
       </c>
-      <c r="D11" s="9" t="s">
-        <v>35</v>
-      </c>
-      <c r="E11" s="9" t="s">
-        <v>36</v>
-      </c>
-      <c r="F11" s="3" t="s">
+      <c r="D14" s="4" t="s">
         <v>60</v>
       </c>
-      <c r="G11" s="10" t="s">
+      <c r="E14" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="F14" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="G14" s="4" t="s">
         <v>27</v>
       </c>
-      <c r="H11" s="10" t="s">
+      <c r="H14" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="I11" s="10" t="s">
-        <v>29</v>
-      </c>
-      <c r="J11" s="14" t="s">
+      <c r="I14" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="J14" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="K14" s="1">
+        <v>344441300</v>
+      </c>
+      <c r="L14" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="M14" s="4" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="15" spans="1:25" ht="14.25" customHeight="1">
+      <c r="B15" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="C15" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="D15" s="4" t="s">
+        <v>60</v>
+      </c>
+      <c r="E15" s="4" t="s">
         <v>61</v>
       </c>
-      <c r="K11" s="10">
-        <v>3.103511752E9</v>
-      </c>
-      <c r="L11" s="10" t="s">
-        <v>39</v>
-      </c>
-      <c r="M11" s="13" t="s">
-        <v>39</v>
-      </c>
-      <c r="N11" s="13" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="12" ht="14.25" customHeight="1">
-      <c r="A12" s="1">
-        <v>11.0</v>
-      </c>
-      <c r="C12" s="9" t="s">
-        <v>62</v>
-      </c>
-      <c r="D12" s="9" t="s">
-        <v>35</v>
-      </c>
-      <c r="E12" s="9" t="s">
-        <v>36</v>
-      </c>
-      <c r="F12" s="3" t="s">
-        <v>63</v>
-      </c>
-      <c r="G12" s="9" t="s">
+      <c r="F15" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="G15" s="4" t="s">
         <v>27</v>
       </c>
-      <c r="H12" s="9" t="s">
+      <c r="H15" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="I12" s="9" t="s">
-        <v>29</v>
-      </c>
-      <c r="J12" s="9" t="s">
+      <c r="I15" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="J15" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="K15" s="4">
+        <v>343222646</v>
+      </c>
+      <c r="L15" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="M15" s="4" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="16" spans="1:25" ht="14.25" customHeight="1">
+      <c r="B16" s="4" t="s">
+        <v>69</v>
+      </c>
+      <c r="C16" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="D16" s="4" t="s">
+        <v>60</v>
+      </c>
+      <c r="E16" s="4" t="s">
+        <v>61</v>
+      </c>
+      <c r="F16" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="G16" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="H16" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="I16" s="4" t="s">
+        <v>70</v>
+      </c>
+      <c r="J16" s="1">
+        <v>3118991142</v>
+      </c>
+      <c r="K16" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="L16" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="M16" s="4" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="17" spans="2:13" ht="14.25" customHeight="1">
+      <c r="B17" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="C17" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="D17" s="4" t="s">
+        <v>60</v>
+      </c>
+      <c r="E17" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="F17" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="G17" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="H17" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="I17" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="J17" s="1">
+        <v>3184778655</v>
+      </c>
+      <c r="K17" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="L17" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="M17" s="4" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="18" spans="2:13" ht="14.25" customHeight="1">
+      <c r="B18" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="C18" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="D18" s="4" t="s">
+        <v>60</v>
+      </c>
+      <c r="E18" s="4" t="s">
+        <v>76</v>
+      </c>
+      <c r="F18" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="G18" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="H18" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="I18" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="J18" s="1">
+        <v>3014076479</v>
+      </c>
+      <c r="K18" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="L18" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="M18" s="4" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="19" spans="2:13" ht="14.25" customHeight="1">
+      <c r="B19" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="C19" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="D19" s="4" t="s">
+        <v>60</v>
+      </c>
+      <c r="E19" s="4" t="s">
+        <v>80</v>
+      </c>
+      <c r="F19" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="G19" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="H19" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="I19" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="J19" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="K19" s="1">
+        <v>343228137</v>
+      </c>
+      <c r="L19" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="M19" s="4" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="20" spans="2:13" ht="14.25" customHeight="1">
+      <c r="B20" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="C20" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="D20" s="4" t="s">
+        <v>60</v>
+      </c>
+      <c r="E20" s="4" t="s">
+        <v>83</v>
+      </c>
+      <c r="F20" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="G20" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="H20" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="I20" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="J20" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="K20" s="1">
+        <v>343456130</v>
+      </c>
+      <c r="L20" s="11" t="s">
+        <v>85</v>
+      </c>
+      <c r="M20" s="4" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="21" spans="2:13" ht="14.25" customHeight="1">
+      <c r="B21" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="C21" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="D21" s="4" t="s">
+        <v>88</v>
+      </c>
+      <c r="E21" s="4" t="s">
+        <v>89</v>
+      </c>
+      <c r="F21" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="G21" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="H21" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="I21" s="4" t="s">
+        <v>90</v>
+      </c>
+      <c r="J21" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="K21" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="L21" s="11" t="s">
+        <v>92</v>
+      </c>
+      <c r="M21" s="12" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="22" spans="2:13" ht="14.25" customHeight="1">
+      <c r="B22" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="C22" s="4" t="s">
+        <v>95</v>
+      </c>
+      <c r="D22" s="4" t="s">
+        <v>96</v>
+      </c>
+      <c r="E22" s="4" t="s">
+        <v>97</v>
+      </c>
+      <c r="F22" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="G22" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="H22" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="I22" s="1" t="s">
+        <v>98</v>
+      </c>
+      <c r="J22" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="K22" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="L22" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="M22" s="4" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="23" spans="2:13" ht="14.25" customHeight="1">
+      <c r="B23" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="C23" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="D23" s="4" t="s">
+        <v>60</v>
+      </c>
+      <c r="E23" s="4" t="s">
+        <v>101</v>
+      </c>
+      <c r="F23" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="G23" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="H23" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="I23" s="1" t="s">
+        <v>102</v>
+      </c>
+      <c r="J23" s="1" t="s">
+        <v>103</v>
+      </c>
+      <c r="K23" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="L23" s="11" t="s">
+        <v>104</v>
+      </c>
+      <c r="M23" s="4" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="24" spans="2:13" ht="14.25" customHeight="1">
+      <c r="B24" s="1" t="s">
+        <v>105</v>
+      </c>
+      <c r="C24" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="D24" s="4" t="s">
+        <v>60</v>
+      </c>
+      <c r="E24" s="4" t="s">
+        <v>106</v>
+      </c>
+      <c r="F24" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="G24" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="H24" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="I24" s="1" t="s">
+        <v>107</v>
+      </c>
+      <c r="J24" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="K24" s="1">
+        <v>343294667</v>
+      </c>
+      <c r="L24" s="11" t="s">
+        <v>108</v>
+      </c>
+      <c r="M24" s="4" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="25" spans="2:13" ht="14.25" customHeight="1">
+      <c r="B25" s="4" t="s">
+        <v>109</v>
+      </c>
+      <c r="C25" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="D25" s="4" t="s">
+        <v>60</v>
+      </c>
+      <c r="E25" s="4" t="s">
+        <v>101</v>
+      </c>
+      <c r="F25" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="G25" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="H25" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="I25" s="1" t="s">
+        <v>110</v>
+      </c>
+      <c r="J25" s="1" t="s">
+        <v>111</v>
+      </c>
+      <c r="K25" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="L25" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="M25" s="4" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="26" spans="2:13" ht="14.25" customHeight="1">
+      <c r="B26" s="1" t="s">
         <v>64</v>
       </c>
-      <c r="K12" s="9">
-        <v>3.137434048E9</v>
-      </c>
-      <c r="L12" s="10" t="s">
-        <v>39</v>
-      </c>
-      <c r="M12" s="10" t="s">
-        <v>39</v>
-      </c>
-      <c r="N12" s="10" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="13" ht="14.25" customHeight="1">
-      <c r="A13" s="1">
-        <v>12.0</v>
-      </c>
-      <c r="C13" s="9" t="s">
-        <v>65</v>
-      </c>
-      <c r="D13" s="9" t="s">
-        <v>35</v>
-      </c>
-      <c r="E13" s="9" t="s">
-        <v>36</v>
-      </c>
-      <c r="F13" s="3" t="s">
-        <v>66</v>
-      </c>
-      <c r="G13" s="9" t="s">
+      <c r="C26" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="D26" s="4" t="s">
+        <v>60</v>
+      </c>
+      <c r="E26" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="F26" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="G26" s="4" t="s">
         <v>27</v>
       </c>
-      <c r="H13" s="9" t="s">
+      <c r="H26" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="I13" s="9" t="s">
-        <v>29</v>
-      </c>
-      <c r="J13" s="15" t="s">
-        <v>67</v>
-      </c>
-      <c r="K13" s="9" t="s">
-        <v>39</v>
-      </c>
-      <c r="L13" s="9" t="s">
-        <v>39</v>
-      </c>
-      <c r="M13" s="9" t="s">
-        <v>39</v>
-      </c>
-      <c r="N13" s="9" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="14" ht="14.25" customHeight="1">
-      <c r="A14" s="1">
-        <v>13.0</v>
-      </c>
-      <c r="C14" s="16" t="s">
-        <v>68</v>
-      </c>
-      <c r="D14" s="9" t="s">
-        <v>69</v>
-      </c>
-      <c r="E14" s="9" t="s">
-        <v>70</v>
-      </c>
-      <c r="F14" s="3" t="s">
-        <v>71</v>
-      </c>
-      <c r="G14" s="9" t="s">
+      <c r="I26" s="4" t="s">
+        <v>112</v>
+      </c>
+      <c r="J26" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="K26" s="1">
+        <v>343011060</v>
+      </c>
+      <c r="L26" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="M26" s="4" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="27" spans="2:13" ht="14.25" customHeight="1">
+      <c r="B27" s="1" t="s">
+        <v>113</v>
+      </c>
+      <c r="C27" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="D27" s="4" t="s">
+        <v>60</v>
+      </c>
+      <c r="E27" s="4" t="s">
+        <v>106</v>
+      </c>
+      <c r="F27" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="G27" s="4" t="s">
         <v>27</v>
       </c>
-      <c r="H14" s="9" t="s">
+      <c r="H27" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="I14" s="9" t="s">
-        <v>29</v>
-      </c>
-      <c r="J14" s="17" t="s">
-        <v>72</v>
-      </c>
-      <c r="K14" s="9" t="s">
-        <v>39</v>
-      </c>
-      <c r="L14" s="9">
-        <v>3.43224172E8</v>
-      </c>
-      <c r="M14" s="18" t="s">
-        <v>73</v>
-      </c>
-      <c r="N14" s="9" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="15" ht="14.25" customHeight="1">
-      <c r="A15" s="1">
-        <v>14.0</v>
-      </c>
-      <c r="C15" s="1" t="s">
-        <v>74</v>
-      </c>
-      <c r="D15" s="9" t="s">
-        <v>69</v>
-      </c>
-      <c r="E15" s="9" t="s">
-        <v>70</v>
-      </c>
-      <c r="F15" s="3" t="s">
-        <v>71</v>
-      </c>
-      <c r="G15" s="9" t="s">
+      <c r="I27" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="J27" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="K27" s="1">
+        <v>342881762</v>
+      </c>
+      <c r="L27" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="M27" s="4" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="28" spans="2:13" ht="14.25" customHeight="1">
+      <c r="B28" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="C28" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="D28" s="4" t="s">
+        <v>60</v>
+      </c>
+      <c r="E28" s="4" t="s">
+        <v>106</v>
+      </c>
+      <c r="F28" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="G28" s="4" t="s">
         <v>27</v>
       </c>
-      <c r="H15" s="9" t="s">
+      <c r="H28" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="I15" s="9" t="s">
-        <v>29</v>
-      </c>
-      <c r="J15" s="17" t="s">
-        <v>75</v>
-      </c>
-      <c r="K15" s="9" t="s">
-        <v>39</v>
-      </c>
-      <c r="L15" s="17">
-        <v>3.444413E8</v>
-      </c>
-      <c r="M15" s="9" t="s">
-        <v>39</v>
-      </c>
-      <c r="N15" s="9" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="16" ht="14.25" customHeight="1">
-      <c r="A16" s="1">
-        <v>15.0</v>
-      </c>
-      <c r="C16" s="1" t="s">
-        <v>76</v>
-      </c>
-      <c r="D16" s="9" t="s">
-        <v>69</v>
-      </c>
-      <c r="E16" s="9" t="s">
-        <v>70</v>
-      </c>
-      <c r="F16" s="9" t="s">
-        <v>71</v>
-      </c>
-      <c r="G16" s="9" t="s">
+      <c r="I28" s="1" t="s">
+        <v>116</v>
+      </c>
+      <c r="J28" s="1" t="s">
+        <v>117</v>
+      </c>
+      <c r="K28" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="L28" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="M28" s="4" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="29" spans="2:13" ht="14.25" customHeight="1">
+      <c r="B29" s="1" t="s">
+        <v>118</v>
+      </c>
+      <c r="C29" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="D29" s="4" t="s">
+        <v>60</v>
+      </c>
+      <c r="E29" s="4" t="s">
+        <v>106</v>
+      </c>
+      <c r="F29" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="G29" s="4" t="s">
         <v>27</v>
       </c>
-      <c r="H16" s="9" t="s">
+      <c r="H29" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="I16" s="9" t="s">
-        <v>29</v>
-      </c>
-      <c r="J16" s="17" t="s">
-        <v>77</v>
-      </c>
-      <c r="K16" s="9" t="s">
-        <v>39</v>
-      </c>
-      <c r="L16" s="9">
-        <v>3.43222646E8</v>
-      </c>
-      <c r="M16" s="18" t="s">
-        <v>78</v>
-      </c>
-      <c r="N16" s="9" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="17" ht="14.25" customHeight="1">
-      <c r="A17" s="1">
-        <v>16.0</v>
-      </c>
-      <c r="C17" s="9" t="s">
-        <v>79</v>
-      </c>
-      <c r="D17" s="9" t="s">
-        <v>69</v>
-      </c>
-      <c r="E17" s="9" t="s">
-        <v>70</v>
-      </c>
-      <c r="F17" s="9" t="s">
-        <v>71</v>
-      </c>
-      <c r="G17" s="9" t="s">
+      <c r="I29" s="1" t="s">
+        <v>119</v>
+      </c>
+      <c r="J29" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="K29" s="1">
+        <v>342888838</v>
+      </c>
+      <c r="L29" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="M29" s="4" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="30" spans="2:13" ht="14.25" customHeight="1">
+      <c r="B30" s="1" t="s">
+        <v>120</v>
+      </c>
+      <c r="C30" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="D30" s="4" t="s">
+        <v>60</v>
+      </c>
+      <c r="E30" s="4" t="s">
+        <v>106</v>
+      </c>
+      <c r="F30" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="G30" s="4" t="s">
         <v>27</v>
       </c>
-      <c r="H17" s="9" t="s">
+      <c r="H30" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="I17" s="9" t="s">
-        <v>29</v>
-      </c>
-      <c r="J17" s="9" t="s">
-        <v>80</v>
-      </c>
-      <c r="K17" s="17">
-        <v>3.118991142E9</v>
-      </c>
-      <c r="L17" s="9" t="s">
-        <v>39</v>
-      </c>
-      <c r="M17" s="1" t="s">
-        <v>81</v>
-      </c>
-      <c r="N17" s="9" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="18" ht="14.25" customHeight="1">
-      <c r="A18" s="1">
-        <v>17.0</v>
-      </c>
-      <c r="C18" s="1" t="s">
-        <v>82</v>
-      </c>
-      <c r="D18" s="9" t="s">
-        <v>69</v>
-      </c>
-      <c r="E18" s="9" t="s">
-        <v>70</v>
-      </c>
-      <c r="F18" s="9" t="s">
-        <v>83</v>
-      </c>
-      <c r="G18" s="9" t="s">
+      <c r="I30" s="1" t="s">
+        <v>121</v>
+      </c>
+      <c r="J30" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="K30" s="1">
+        <v>343019109</v>
+      </c>
+      <c r="L30" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="M30" s="4" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="31" spans="2:13" ht="14.25" customHeight="1">
+      <c r="B31" s="1" t="s">
+        <v>122</v>
+      </c>
+      <c r="C31" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="D31" s="4" t="s">
+        <v>123</v>
+      </c>
+      <c r="E31" s="4" t="s">
+        <v>124</v>
+      </c>
+      <c r="F31" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="G31" s="4" t="s">
         <v>27</v>
       </c>
-      <c r="H18" s="9" t="s">
+      <c r="H31" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="I18" s="9" t="s">
-        <v>29</v>
-      </c>
-      <c r="J18" s="17" t="s">
-        <v>84</v>
-      </c>
-      <c r="K18" s="17">
-        <v>3.184778655E9</v>
-      </c>
-      <c r="L18" s="9" t="s">
-        <v>39</v>
-      </c>
-      <c r="M18" s="9" t="s">
-        <v>39</v>
-      </c>
-      <c r="N18" s="9" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="19" ht="14.25" customHeight="1">
-      <c r="A19" s="1">
-        <v>18.0</v>
-      </c>
-      <c r="C19" s="1" t="s">
-        <v>85</v>
-      </c>
-      <c r="D19" s="9" t="s">
-        <v>69</v>
-      </c>
-      <c r="E19" s="9" t="s">
-        <v>70</v>
-      </c>
-      <c r="F19" s="9" t="s">
-        <v>86</v>
-      </c>
-      <c r="G19" s="9" t="s">
+      <c r="I31" s="1" t="s">
+        <v>125</v>
+      </c>
+      <c r="J31" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="K31" s="1" t="s">
+        <v>126</v>
+      </c>
+      <c r="L31" s="13" t="s">
+        <v>30</v>
+      </c>
+      <c r="M31" s="4" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="32" spans="2:13" ht="14.25" customHeight="1">
+      <c r="B32" s="1" t="s">
+        <v>127</v>
+      </c>
+      <c r="C32" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="D32" s="4" t="s">
+        <v>60</v>
+      </c>
+      <c r="E32" s="4" t="s">
+        <v>106</v>
+      </c>
+      <c r="F32" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="G32" s="4" t="s">
         <v>27</v>
       </c>
-      <c r="H19" s="9" t="s">
+      <c r="H32" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="I19" s="9" t="s">
-        <v>29</v>
-      </c>
-      <c r="J19" s="17" t="s">
-        <v>87</v>
-      </c>
-      <c r="K19" s="17">
-        <v>3.014076479E9</v>
-      </c>
-      <c r="L19" s="9" t="s">
-        <v>39</v>
-      </c>
-      <c r="M19" s="1" t="s">
-        <v>88</v>
-      </c>
-      <c r="N19" s="9" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="20" ht="14.25" customHeight="1">
-      <c r="A20" s="9">
-        <v>19.0</v>
-      </c>
-      <c r="C20" s="1" t="s">
-        <v>89</v>
-      </c>
-      <c r="D20" s="9" t="s">
-        <v>69</v>
-      </c>
-      <c r="E20" s="9" t="s">
-        <v>70</v>
-      </c>
-      <c r="F20" s="9" t="s">
-        <v>90</v>
-      </c>
-      <c r="G20" s="9" t="s">
+      <c r="I32" t="s">
+        <v>128</v>
+      </c>
+      <c r="J32" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="K32" s="1" t="s">
+        <v>129</v>
+      </c>
+      <c r="L32" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="M32" s="4" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="33" spans="2:13" ht="14.25" customHeight="1">
+      <c r="B33" s="1" t="s">
+        <v>130</v>
+      </c>
+      <c r="C33" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="D33" s="4" t="s">
+        <v>60</v>
+      </c>
+      <c r="E33" s="4" t="s">
+        <v>106</v>
+      </c>
+      <c r="F33" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="G33" s="4" t="s">
         <v>27</v>
       </c>
-      <c r="H20" s="9" t="s">
+      <c r="H33" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="I20" s="9" t="s">
-        <v>29</v>
-      </c>
-      <c r="J20" s="17" t="s">
-        <v>91</v>
-      </c>
-      <c r="K20" s="9" t="s">
-        <v>39</v>
-      </c>
-      <c r="L20" s="17">
-        <v>3.43228137E8</v>
-      </c>
-      <c r="M20" s="9" t="s">
-        <v>39</v>
-      </c>
-      <c r="N20" s="9" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="21" ht="14.25" customHeight="1">
-      <c r="A21" s="9">
-        <v>20.0</v>
-      </c>
-      <c r="C21" s="1" t="s">
-        <v>92</v>
-      </c>
-      <c r="D21" s="9" t="s">
-        <v>69</v>
-      </c>
-      <c r="E21" s="9" t="s">
-        <v>70</v>
-      </c>
-      <c r="F21" s="9" t="s">
-        <v>93</v>
-      </c>
-      <c r="G21" s="9" t="s">
+      <c r="I33" t="s">
+        <v>131</v>
+      </c>
+      <c r="J33" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="K33" s="1">
+        <v>342881815</v>
+      </c>
+      <c r="L33" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="M33" s="4" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="34" spans="2:13" ht="14.25" customHeight="1">
+      <c r="B34" s="1" t="s">
+        <v>132</v>
+      </c>
+      <c r="C34" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="D34" s="4" t="s">
+        <v>60</v>
+      </c>
+      <c r="E34" s="4" t="s">
+        <v>106</v>
+      </c>
+      <c r="F34" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="G34" s="4" t="s">
         <v>27</v>
       </c>
-      <c r="H21" s="9" t="s">
+      <c r="H34" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="I21" s="9" t="s">
-        <v>29</v>
-      </c>
-      <c r="J21" s="17" t="s">
-        <v>94</v>
-      </c>
-      <c r="K21" s="9" t="s">
-        <v>39</v>
-      </c>
-      <c r="L21" s="17">
-        <v>3.4345613E8</v>
-      </c>
-      <c r="M21" s="19" t="s">
-        <v>95</v>
-      </c>
-      <c r="N21" s="9" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="22" ht="14.25" customHeight="1">
-      <c r="A22" s="9">
-        <v>21.0</v>
-      </c>
-      <c r="C22" s="1" t="s">
+      <c r="I34" s="1" t="s">
+        <v>133</v>
+      </c>
+      <c r="J34" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="K34" s="1">
+        <v>343221810</v>
+      </c>
+      <c r="L34" s="11" t="s">
+        <v>134</v>
+      </c>
+      <c r="M34" s="4" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="35" spans="2:13" ht="14.25" customHeight="1">
+      <c r="B35" s="1" t="s">
+        <v>135</v>
+      </c>
+      <c r="C35" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="D35" s="4" t="s">
+        <v>60</v>
+      </c>
+      <c r="E35" s="4" t="s">
+        <v>106</v>
+      </c>
+      <c r="F35" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="G35" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="H35" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="I35" s="1" t="s">
+        <v>136</v>
+      </c>
+      <c r="J35" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="K35" s="1" t="s">
+        <v>137</v>
+      </c>
+      <c r="L35" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="M35" s="4" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="36" spans="2:13" ht="14.25" customHeight="1">
+      <c r="B36" s="1" t="s">
+        <v>138</v>
+      </c>
+      <c r="C36" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="D36" s="4" t="s">
+        <v>60</v>
+      </c>
+      <c r="E36" s="4" t="s">
+        <v>106</v>
+      </c>
+      <c r="F36" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="G36" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="H36" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="I36" t="s">
+        <v>139</v>
+      </c>
+      <c r="J36" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="K36" s="1">
+        <v>344488897</v>
+      </c>
+      <c r="L36" s="11" t="s">
+        <v>140</v>
+      </c>
+      <c r="M36" s="4" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="37" spans="2:13" ht="14.25" customHeight="1">
+      <c r="B37" s="1" t="s">
+        <v>141</v>
+      </c>
+      <c r="C37" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="D37" s="4" t="s">
+        <v>60</v>
+      </c>
+      <c r="E37" s="4" t="s">
+        <v>106</v>
+      </c>
+      <c r="F37" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="G37" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="H37" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="I37" s="1" t="s">
+        <v>142</v>
+      </c>
+      <c r="J37" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="K37" s="1">
+        <v>344447374</v>
+      </c>
+      <c r="L37" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="M37" s="4" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="38" spans="2:13" ht="14.25" customHeight="1">
+      <c r="B38" s="1" t="s">
+        <v>143</v>
+      </c>
+      <c r="C38" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="D38" s="4" t="s">
+        <v>144</v>
+      </c>
+      <c r="E38" s="4" t="s">
+        <v>145</v>
+      </c>
+      <c r="F38" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="G38" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="H38" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="I38" s="4" t="s">
+        <v>146</v>
+      </c>
+      <c r="J38" s="1" t="s">
+        <v>147</v>
+      </c>
+      <c r="K38" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="L38" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="M38" s="4" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="39" spans="2:13" ht="14.25" customHeight="1">
+      <c r="B39" s="1" t="s">
+        <v>148</v>
+      </c>
+      <c r="C39" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="D39" s="4" t="s">
+        <v>60</v>
+      </c>
+      <c r="E39" s="4" t="s">
+        <v>106</v>
+      </c>
+      <c r="F39" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="G39" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="H39" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="I39" s="1" t="s">
+        <v>149</v>
+      </c>
+      <c r="J39" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="K39" s="1">
+        <v>342888204</v>
+      </c>
+      <c r="L39" s="11" t="s">
+        <v>150</v>
+      </c>
+      <c r="M39" s="4" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="40" spans="2:13" ht="14.25" customHeight="1">
+      <c r="B40" s="1" t="s">
+        <v>151</v>
+      </c>
+      <c r="C40" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="D40" s="4" t="s">
+        <v>60</v>
+      </c>
+      <c r="E40" s="4" t="s">
+        <v>152</v>
+      </c>
+      <c r="F40" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="G40" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="H40" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="I40" t="s">
+        <v>153</v>
+      </c>
+      <c r="J40" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="K40" s="1">
+        <v>343015943</v>
+      </c>
+      <c r="L40" s="11" t="s">
+        <v>154</v>
+      </c>
+      <c r="M40" s="4" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="41" spans="2:13" ht="14.25" customHeight="1">
+      <c r="B41" s="1" t="s">
+        <v>155</v>
+      </c>
+      <c r="C41" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="D41" s="4" t="s">
+        <v>60</v>
+      </c>
+      <c r="E41" s="4" t="s">
+        <v>156</v>
+      </c>
+      <c r="F41" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="G41" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="H41" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="I41" s="1" t="s">
+        <v>157</v>
+      </c>
+      <c r="J41" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="K41" s="1">
+        <v>342884860</v>
+      </c>
+      <c r="L41" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="M41" s="4" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="42" spans="2:13" ht="14.25" customHeight="1">
+      <c r="B42" s="1" t="s">
+        <v>158</v>
+      </c>
+      <c r="C42" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="D42" s="4" t="s">
+        <v>60</v>
+      </c>
+      <c r="E42" s="4" t="s">
+        <v>106</v>
+      </c>
+      <c r="F42" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="G42" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="H42" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="I42" t="s">
+        <v>159</v>
+      </c>
+      <c r="J42" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="K42" s="1">
+        <v>342884574</v>
+      </c>
+      <c r="L42" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="M42" s="4" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="43" spans="2:13" ht="14.25" customHeight="1">
+      <c r="B43" s="1" t="s">
+        <v>160</v>
+      </c>
+      <c r="C43" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="D43" s="4" t="s">
+        <v>60</v>
+      </c>
+      <c r="E43" s="4" t="s">
+        <v>106</v>
+      </c>
+      <c r="F43" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="G43" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="H43" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="I43" s="1" t="s">
+        <v>161</v>
+      </c>
+      <c r="J43" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="K43" s="1">
+        <v>346129961</v>
+      </c>
+      <c r="L43" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="M43" s="4" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="44" spans="2:13" ht="14.25" customHeight="1">
+      <c r="B44" s="1" t="s">
+        <v>162</v>
+      </c>
+      <c r="C44" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="D44" s="4" t="s">
+        <v>60</v>
+      </c>
+      <c r="E44" s="4" t="s">
+        <v>106</v>
+      </c>
+      <c r="F44" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="G44" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="H44" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="I44" t="s">
+        <v>163</v>
+      </c>
+      <c r="J44" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="K44" s="1">
+        <v>6046046600</v>
+      </c>
+      <c r="L44" s="1" t="s">
+        <v>164</v>
+      </c>
+      <c r="M44" s="4" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="45" spans="2:13" ht="14.25" customHeight="1">
+      <c r="B45" s="1" t="s">
+        <v>165</v>
+      </c>
+      <c r="C45" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="D45" s="4" t="s">
+        <v>60</v>
+      </c>
+      <c r="E45" s="4" t="s">
+        <v>106</v>
+      </c>
+      <c r="F45" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="G45" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="H45" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="I45" s="1" t="s">
+        <v>166</v>
+      </c>
+      <c r="J45" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="K45" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="L45" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="M45" s="4" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="46" spans="2:13" ht="14.25" customHeight="1">
+      <c r="B46" s="1" t="s">
+        <v>167</v>
+      </c>
+      <c r="C46" s="4" t="s">
+        <v>168</v>
+      </c>
+      <c r="D46" s="4" t="s">
+        <v>169</v>
+      </c>
+      <c r="E46" s="4" t="s">
+        <v>170</v>
+      </c>
+      <c r="F46" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="G46" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="H46" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="I46" t="s">
+        <v>171</v>
+      </c>
+      <c r="J46" s="4" t="s">
+        <v>172</v>
+      </c>
+      <c r="K46" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="L46" s="4" t="s">
+        <v>173</v>
+      </c>
+      <c r="M46" s="4" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="47" spans="2:13" ht="14.25" customHeight="1">
+      <c r="B47" s="1" t="s">
+        <v>174</v>
+      </c>
+      <c r="C47" s="4" t="s">
+        <v>168</v>
+      </c>
+      <c r="D47" s="4" t="s">
+        <v>169</v>
+      </c>
+      <c r="E47" s="4" t="s">
+        <v>175</v>
+      </c>
+      <c r="F47" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="G47" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="H47" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="I47" t="s">
+        <v>176</v>
+      </c>
+      <c r="J47" s="4" t="s">
+        <v>177</v>
+      </c>
+      <c r="K47" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="L47" s="4" t="s">
+        <v>178</v>
+      </c>
+      <c r="M47" s="4" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="48" spans="2:13" ht="14.25" customHeight="1">
+      <c r="B48" s="1" t="s">
+        <v>179</v>
+      </c>
+      <c r="C48" s="4" t="s">
+        <v>168</v>
+      </c>
+      <c r="D48" s="4" t="s">
+        <v>169</v>
+      </c>
+      <c r="E48" s="4" t="s">
+        <v>180</v>
+      </c>
+      <c r="F48" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="G48" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="H48" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="I48" t="s">
+        <v>181</v>
+      </c>
+      <c r="J48" s="4" t="s">
+        <v>182</v>
+      </c>
+      <c r="K48" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="L48" s="4" t="s">
+        <v>183</v>
+      </c>
+      <c r="M48" s="4" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="49" spans="2:13" ht="14.25" customHeight="1">
+      <c r="B49" s="1" t="s">
+        <v>184</v>
+      </c>
+      <c r="C49" s="4" t="s">
+        <v>168</v>
+      </c>
+      <c r="D49" s="4" t="s">
+        <v>169</v>
+      </c>
+      <c r="E49" s="4" t="s">
+        <v>185</v>
+      </c>
+      <c r="F49" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="G49" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="H49" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="I49" s="1" t="s">
+        <v>186</v>
+      </c>
+      <c r="J49" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="K49" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="L49" s="4" t="s">
+        <v>187</v>
+      </c>
+      <c r="M49" s="4" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="50" spans="2:13" ht="14.25" customHeight="1">
+      <c r="B50" s="1" t="s">
+        <v>188</v>
+      </c>
+      <c r="C50" s="4" t="s">
+        <v>168</v>
+      </c>
+      <c r="D50" s="4" t="s">
+        <v>169</v>
+      </c>
+      <c r="E50" s="4" t="s">
+        <v>189</v>
+      </c>
+      <c r="F50" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="G50" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="H50" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="I50" t="s">
+        <v>190</v>
+      </c>
+      <c r="J50" s="4" t="s">
+        <v>191</v>
+      </c>
+      <c r="K50" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="L50" s="4" t="s">
+        <v>192</v>
+      </c>
+      <c r="M50" s="4" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="51" spans="2:13" ht="14.25" customHeight="1">
+      <c r="B51" s="1" t="s">
+        <v>193</v>
+      </c>
+      <c r="C51" s="4" t="s">
+        <v>168</v>
+      </c>
+      <c r="D51" s="4" t="s">
+        <v>169</v>
+      </c>
+      <c r="E51" s="4" t="s">
+        <v>194</v>
+      </c>
+      <c r="F51" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="G51" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="H51" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="J51" s="4" t="s">
+        <v>195</v>
+      </c>
+      <c r="K51" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="L51" s="4" t="s">
+        <v>196</v>
+      </c>
+      <c r="M51" s="4" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="52" spans="2:13" ht="14.25" customHeight="1">
+      <c r="B52" s="1" t="s">
+        <v>197</v>
+      </c>
+      <c r="C52" s="4" t="s">
+        <v>168</v>
+      </c>
+      <c r="D52" s="4" t="s">
+        <v>198</v>
+      </c>
+      <c r="E52" s="4" t="s">
+        <v>199</v>
+      </c>
+      <c r="F52" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="G52" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="H52" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="I52" s="1" t="s">
+        <v>252</v>
+      </c>
+      <c r="J52" s="14">
+        <v>342880159</v>
+      </c>
+      <c r="K52" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="L52" s="4" t="s">
+        <v>200</v>
+      </c>
+      <c r="M52" s="4" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="53" spans="2:13" ht="14.25" customHeight="1">
+      <c r="B53" s="1" t="s">
+        <v>201</v>
+      </c>
+      <c r="C53" s="4" t="s">
+        <v>168</v>
+      </c>
+      <c r="D53" s="4" t="s">
+        <v>198</v>
+      </c>
+      <c r="E53" s="4" t="s">
+        <v>199</v>
+      </c>
+      <c r="F53" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="G53" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="H53" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="I53" s="1" t="s">
+        <v>202</v>
+      </c>
+      <c r="J53" s="14">
+        <v>3045383728</v>
+      </c>
+      <c r="K53" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="L53" s="4" t="s">
+        <v>203</v>
+      </c>
+      <c r="M53" s="4" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="54" spans="2:13" ht="14.25" customHeight="1">
+      <c r="B54" s="1" t="s">
+        <v>205</v>
+      </c>
+      <c r="C54" s="4" t="s">
+        <v>168</v>
+      </c>
+      <c r="D54" s="4" t="s">
+        <v>198</v>
+      </c>
+      <c r="E54" s="4" t="s">
+        <v>199</v>
+      </c>
+      <c r="F54" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="G54" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="H54" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="I54" s="4" t="s">
+        <v>206</v>
+      </c>
+      <c r="J54" s="14">
+        <v>3002730515</v>
+      </c>
+      <c r="K54" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="L54" s="4" t="s">
+        <v>207</v>
+      </c>
+      <c r="M54" s="15" t="s">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="55" spans="2:13" ht="14.25" customHeight="1">
+      <c r="B55" s="1" t="s">
+        <v>209</v>
+      </c>
+      <c r="C55" s="4" t="s">
+        <v>168</v>
+      </c>
+      <c r="D55" s="4" t="s">
+        <v>198</v>
+      </c>
+      <c r="E55" s="4" t="s">
+        <v>199</v>
+      </c>
+      <c r="F55" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="G55" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="H55" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="I55" s="1" t="s">
+        <v>210</v>
+      </c>
+      <c r="J55" s="14">
+        <v>3022705056</v>
+      </c>
+      <c r="K55" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="L55" s="4" t="s">
+        <v>211</v>
+      </c>
+      <c r="M55" s="15" t="s">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="56" spans="2:13" ht="14.25" customHeight="1">
+      <c r="B56" s="1" t="s">
+        <v>213</v>
+      </c>
+      <c r="C56" s="4" t="s">
+        <v>168</v>
+      </c>
+      <c r="D56" s="4" t="s">
+        <v>198</v>
+      </c>
+      <c r="E56" s="4" t="s">
+        <v>199</v>
+      </c>
+      <c r="F56" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="G56" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="H56" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="I56" s="1" t="s">
+        <v>214</v>
+      </c>
+      <c r="J56" s="14">
+        <v>3003568587</v>
+      </c>
+      <c r="K56" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="L56" s="4" t="s">
+        <v>215</v>
+      </c>
+      <c r="M56" s="4" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="57" spans="2:13" ht="14.25" customHeight="1">
+      <c r="B57" s="1" t="s">
+        <v>216</v>
+      </c>
+      <c r="C57" s="4" t="s">
+        <v>168</v>
+      </c>
+      <c r="D57" s="4" t="s">
+        <v>198</v>
+      </c>
+      <c r="E57" s="4" t="s">
+        <v>199</v>
+      </c>
+      <c r="F57" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="G57" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="H57" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="I57" s="1" t="s">
+        <v>217</v>
+      </c>
+      <c r="J57" s="14" t="s">
+        <v>30</v>
+      </c>
+      <c r="K57" s="14">
+        <v>343665019</v>
+      </c>
+      <c r="L57" s="4" t="s">
+        <v>218</v>
+      </c>
+      <c r="M57" s="4" t="s">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="58" spans="2:13" ht="14.25" customHeight="1">
+      <c r="B58" s="1" t="s">
+        <v>220</v>
+      </c>
+      <c r="C58" s="4" t="s">
+        <v>168</v>
+      </c>
+      <c r="D58" s="4" t="s">
+        <v>198</v>
+      </c>
+      <c r="E58" s="4" t="s">
+        <v>199</v>
+      </c>
+      <c r="F58" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="G58" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="H58" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="I58" t="s">
+        <v>221</v>
+      </c>
+      <c r="J58" s="14" t="s">
+        <v>30</v>
+      </c>
+      <c r="K58" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="L58" s="4" t="s">
+        <v>222</v>
+      </c>
+      <c r="M58" s="4" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="59" spans="2:13" ht="14.25" customHeight="1">
+      <c r="B59" s="1" t="s">
+        <v>223</v>
+      </c>
+      <c r="C59" s="4" t="s">
+        <v>168</v>
+      </c>
+      <c r="D59" s="4" t="s">
+        <v>198</v>
+      </c>
+      <c r="E59" s="4" t="s">
+        <v>199</v>
+      </c>
+      <c r="F59" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="G59" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="H59" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="I59" s="1" t="s">
+        <v>253</v>
+      </c>
+      <c r="J59" s="14">
+        <v>343660313</v>
+      </c>
+      <c r="K59" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="L59" s="4" t="s">
+        <v>224</v>
+      </c>
+      <c r="M59" s="4" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="60" spans="2:13" ht="14.25" customHeight="1">
+      <c r="B60" s="1" t="s">
+        <v>225</v>
+      </c>
+      <c r="C60" s="4" t="s">
+        <v>168</v>
+      </c>
+      <c r="D60" s="4" t="s">
+        <v>198</v>
+      </c>
+      <c r="E60" s="4" t="s">
+        <v>199</v>
+      </c>
+      <c r="F60" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="G60" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="H60" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="I60" s="1" t="s">
+        <v>226</v>
+      </c>
+      <c r="J60" s="14">
+        <v>3003455457</v>
+      </c>
+      <c r="K60" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="L60" s="4" t="s">
+        <v>227</v>
+      </c>
+      <c r="M60" s="4" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="61" spans="2:13" ht="14.25" customHeight="1">
+      <c r="B61" s="1" t="s">
+        <v>229</v>
+      </c>
+      <c r="C61" s="4" t="s">
+        <v>168</v>
+      </c>
+      <c r="D61" s="4" t="s">
+        <v>198</v>
+      </c>
+      <c r="E61" s="4" t="s">
+        <v>199</v>
+      </c>
+      <c r="F61" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="G61" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="H61" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="I61" s="1" t="s">
+        <v>230</v>
+      </c>
+      <c r="J61" s="14">
+        <v>3185108864</v>
+      </c>
+      <c r="K61" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="L61" s="4" t="s">
+        <v>231</v>
+      </c>
+      <c r="M61" s="4" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="62" spans="2:13" ht="14.25" customHeight="1">
+      <c r="B62" t="s">
+        <v>233</v>
+      </c>
+      <c r="C62" t="s">
         <v>96</v>
       </c>
-      <c r="D22" s="9" t="s">
-        <v>97</v>
-      </c>
-      <c r="E22" s="9" t="s">
-        <v>98</v>
-      </c>
-      <c r="F22" s="9" t="s">
-        <v>99</v>
-      </c>
-      <c r="G22" s="9" t="s">
-        <v>27</v>
-      </c>
-      <c r="H22" s="9" t="s">
-        <v>28</v>
-      </c>
-      <c r="I22" s="9" t="s">
-        <v>29</v>
-      </c>
-      <c r="J22" s="9" t="s">
-        <v>100</v>
-      </c>
-      <c r="K22" s="1" t="s">
-        <v>101</v>
-      </c>
-      <c r="L22" s="9" t="s">
-        <v>39</v>
-      </c>
-      <c r="M22" s="19" t="s">
-        <v>102</v>
-      </c>
-      <c r="N22" s="20" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="23" ht="14.25" customHeight="1">
-      <c r="A23" s="9">
-        <v>22.0</v>
-      </c>
-      <c r="C23" s="1" t="s">
-        <v>104</v>
-      </c>
-      <c r="D23" s="9" t="s">
-        <v>105</v>
-      </c>
-      <c r="E23" s="9" t="s">
-        <v>106</v>
-      </c>
-      <c r="F23" s="9" t="s">
-        <v>107</v>
-      </c>
-      <c r="G23" s="9" t="s">
-        <v>27</v>
-      </c>
-      <c r="H23" s="9" t="s">
-        <v>28</v>
-      </c>
-      <c r="I23" s="9" t="s">
-        <v>29</v>
-      </c>
-      <c r="J23" s="17" t="s">
-        <v>108</v>
-      </c>
-      <c r="K23" s="1" t="s">
-        <v>109</v>
-      </c>
-      <c r="L23" s="9" t="s">
-        <v>39</v>
-      </c>
-      <c r="M23" s="9" t="s">
-        <v>39</v>
-      </c>
-      <c r="N23" s="9" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="24" ht="14.25" customHeight="1">
-      <c r="A24" s="9">
-        <v>23.0</v>
-      </c>
-      <c r="C24" s="1" t="s">
-        <v>110</v>
-      </c>
-      <c r="D24" s="9" t="s">
-        <v>69</v>
-      </c>
-      <c r="E24" s="9" t="s">
-        <v>70</v>
-      </c>
-      <c r="F24" s="9" t="s">
-        <v>111</v>
-      </c>
-      <c r="G24" s="9" t="s">
-        <v>27</v>
-      </c>
-      <c r="H24" s="9" t="s">
-        <v>28</v>
-      </c>
-      <c r="I24" s="9" t="s">
-        <v>29</v>
-      </c>
-      <c r="J24" s="17" t="s">
-        <v>112</v>
-      </c>
-      <c r="K24" s="1" t="s">
-        <v>113</v>
-      </c>
-      <c r="L24" s="9" t="s">
-        <v>39</v>
-      </c>
-      <c r="M24" s="19" t="s">
-        <v>114</v>
-      </c>
-      <c r="N24" s="9" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="25" ht="14.25" customHeight="1">
-      <c r="A25" s="9">
-        <v>24.0</v>
-      </c>
-      <c r="C25" s="1" t="s">
-        <v>115</v>
-      </c>
-      <c r="D25" s="9" t="s">
-        <v>69</v>
-      </c>
-      <c r="E25" s="9" t="s">
-        <v>70</v>
-      </c>
-      <c r="F25" s="9" t="s">
-        <v>116</v>
-      </c>
-      <c r="G25" s="9" t="s">
-        <v>27</v>
-      </c>
-      <c r="H25" s="9" t="s">
-        <v>28</v>
-      </c>
-      <c r="I25" s="9" t="s">
-        <v>29</v>
-      </c>
-      <c r="J25" s="17" t="s">
-        <v>117</v>
-      </c>
-      <c r="K25" s="9" t="s">
-        <v>39</v>
-      </c>
-      <c r="L25" s="17">
-        <v>3.43294667E8</v>
-      </c>
-      <c r="M25" s="19" t="s">
-        <v>118</v>
-      </c>
-      <c r="N25" s="9" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="26" ht="14.25" customHeight="1">
-      <c r="A26" s="9">
-        <v>25.0</v>
-      </c>
-      <c r="C26" s="9" t="s">
-        <v>119</v>
-      </c>
-      <c r="D26" s="9" t="s">
-        <v>69</v>
-      </c>
-      <c r="E26" s="9" t="s">
-        <v>70</v>
-      </c>
-      <c r="F26" s="9" t="s">
-        <v>111</v>
-      </c>
-      <c r="G26" s="9" t="s">
-        <v>27</v>
-      </c>
-      <c r="H26" s="9" t="s">
-        <v>28</v>
-      </c>
-      <c r="I26" s="9" t="s">
-        <v>29</v>
-      </c>
-      <c r="J26" s="17" t="s">
-        <v>120</v>
-      </c>
-      <c r="K26" s="1" t="s">
-        <v>121</v>
-      </c>
-      <c r="L26" s="9" t="s">
-        <v>39</v>
-      </c>
-      <c r="M26" s="9" t="s">
-        <v>39</v>
-      </c>
-      <c r="N26" s="9" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="27" ht="14.25" customHeight="1">
-      <c r="A27" s="9">
-        <v>26.0</v>
-      </c>
-      <c r="C27" s="1" t="s">
-        <v>74</v>
-      </c>
-      <c r="D27" s="9" t="s">
-        <v>69</v>
-      </c>
-      <c r="E27" s="9" t="s">
-        <v>70</v>
-      </c>
-      <c r="F27" s="3" t="s">
-        <v>71</v>
-      </c>
-      <c r="G27" s="9" t="s">
-        <v>27</v>
-      </c>
-      <c r="H27" s="9" t="s">
-        <v>28</v>
-      </c>
-      <c r="I27" s="9" t="s">
-        <v>29</v>
-      </c>
-      <c r="J27" s="9" t="s">
-        <v>122</v>
-      </c>
-      <c r="K27" s="9" t="s">
-        <v>39</v>
-      </c>
-      <c r="L27" s="17">
-        <v>3.4301106E8</v>
-      </c>
-      <c r="M27" s="9" t="s">
-        <v>39</v>
-      </c>
-      <c r="N27" s="9" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="28" ht="14.25" customHeight="1">
-      <c r="A28" s="9">
-        <v>27.0</v>
-      </c>
-      <c r="C28" s="1" t="s">
-        <v>123</v>
-      </c>
-      <c r="D28" s="9" t="s">
-        <v>69</v>
-      </c>
-      <c r="E28" s="9" t="s">
-        <v>70</v>
-      </c>
-      <c r="F28" s="9" t="s">
-        <v>116</v>
-      </c>
-      <c r="G28" s="9" t="s">
-        <v>27</v>
-      </c>
-      <c r="H28" s="9" t="s">
-        <v>28</v>
-      </c>
-      <c r="I28" s="9" t="s">
-        <v>29</v>
-      </c>
-      <c r="J28" s="17" t="s">
-        <v>124</v>
-      </c>
-      <c r="K28" s="9" t="s">
-        <v>39</v>
-      </c>
-      <c r="L28" s="17">
-        <v>3.42881762E8</v>
-      </c>
-      <c r="M28" s="9" t="s">
-        <v>39</v>
-      </c>
-      <c r="N28" s="9" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="29" ht="14.25" customHeight="1">
-      <c r="A29" s="9">
-        <v>28.0</v>
-      </c>
-      <c r="C29" s="1" t="s">
-        <v>125</v>
-      </c>
-      <c r="D29" s="9" t="s">
-        <v>69</v>
-      </c>
-      <c r="E29" s="9" t="s">
-        <v>70</v>
-      </c>
-      <c r="F29" s="9" t="s">
-        <v>116</v>
-      </c>
-      <c r="G29" s="9" t="s">
-        <v>27</v>
-      </c>
-      <c r="H29" s="9" t="s">
-        <v>28</v>
-      </c>
-      <c r="I29" s="9" t="s">
-        <v>29</v>
-      </c>
-      <c r="J29" s="17" t="s">
-        <v>126</v>
-      </c>
-      <c r="K29" s="1" t="s">
-        <v>127</v>
-      </c>
-      <c r="L29" s="9" t="s">
-        <v>39</v>
-      </c>
-      <c r="M29" s="9" t="s">
-        <v>39</v>
-      </c>
-      <c r="N29" s="9" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="30" ht="14.25" customHeight="1">
-      <c r="A30" s="9">
-        <v>29.0</v>
-      </c>
-      <c r="C30" s="1" t="s">
-        <v>128</v>
-      </c>
-      <c r="D30" s="9" t="s">
-        <v>69</v>
-      </c>
-      <c r="E30" s="9" t="s">
-        <v>70</v>
-      </c>
-      <c r="F30" s="9" t="s">
-        <v>116</v>
-      </c>
-      <c r="G30" s="9" t="s">
-        <v>27</v>
-      </c>
-      <c r="H30" s="9" t="s">
-        <v>28</v>
-      </c>
-      <c r="I30" s="9" t="s">
-        <v>29</v>
-      </c>
-      <c r="J30" s="17" t="s">
-        <v>129</v>
-      </c>
-      <c r="K30" s="9" t="s">
-        <v>39</v>
-      </c>
-      <c r="L30" s="17">
-        <v>3.42888838E8</v>
-      </c>
-      <c r="M30" s="9" t="s">
-        <v>39</v>
-      </c>
-      <c r="N30" s="9" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="31" ht="14.25" customHeight="1">
-      <c r="A31" s="9">
-        <v>30.0</v>
-      </c>
-      <c r="C31" s="1" t="s">
-        <v>130</v>
-      </c>
-      <c r="D31" s="9" t="s">
-        <v>69</v>
-      </c>
-      <c r="E31" s="9" t="s">
-        <v>70</v>
-      </c>
-      <c r="F31" s="9" t="s">
-        <v>116</v>
-      </c>
-      <c r="G31" s="9" t="s">
-        <v>27</v>
-      </c>
-      <c r="H31" s="9" t="s">
-        <v>28</v>
-      </c>
-      <c r="I31" s="9" t="s">
-        <v>29</v>
-      </c>
-      <c r="J31" s="17" t="s">
-        <v>131</v>
-      </c>
-      <c r="K31" s="9" t="s">
-        <v>39</v>
-      </c>
-      <c r="L31" s="17">
-        <v>3.43019109E8</v>
-      </c>
-      <c r="M31" s="9" t="s">
-        <v>39</v>
-      </c>
-      <c r="N31" s="9" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="32" ht="14.25" customHeight="1">
-      <c r="A32" s="9">
-        <v>31.0</v>
-      </c>
-      <c r="C32" s="1" t="s">
-        <v>132</v>
-      </c>
-      <c r="D32" s="9" t="s">
-        <v>69</v>
-      </c>
-      <c r="E32" s="9" t="s">
-        <v>133</v>
-      </c>
-      <c r="F32" s="9" t="s">
-        <v>134</v>
-      </c>
-      <c r="G32" s="9" t="s">
-        <v>27</v>
-      </c>
-      <c r="H32" s="9" t="s">
-        <v>28</v>
-      </c>
-      <c r="I32" s="9" t="s">
-        <v>29</v>
-      </c>
-      <c r="J32" s="17" t="s">
-        <v>135</v>
-      </c>
-      <c r="K32" s="9" t="s">
-        <v>39</v>
-      </c>
-      <c r="L32" s="1" t="s">
-        <v>136</v>
-      </c>
-      <c r="M32" s="21" t="s">
-        <v>39</v>
-      </c>
-      <c r="N32" s="9" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="33" ht="14.25" customHeight="1">
-      <c r="A33" s="9">
-        <v>32.0</v>
-      </c>
-      <c r="C33" s="1" t="s">
-        <v>137</v>
-      </c>
-      <c r="D33" s="9" t="s">
-        <v>69</v>
-      </c>
-      <c r="E33" s="9" t="s">
-        <v>70</v>
-      </c>
-      <c r="F33" s="9" t="s">
-        <v>116</v>
-      </c>
-      <c r="G33" s="9" t="s">
-        <v>27</v>
-      </c>
-      <c r="H33" s="9" t="s">
-        <v>28</v>
-      </c>
-      <c r="I33" s="9" t="s">
-        <v>29</v>
-      </c>
-      <c r="J33" s="17" t="s">
-        <v>138</v>
-      </c>
-      <c r="K33" s="9" t="s">
-        <v>39</v>
-      </c>
-      <c r="L33" s="1" t="s">
-        <v>139</v>
-      </c>
-      <c r="M33" s="9" t="s">
-        <v>39</v>
-      </c>
-      <c r="N33" s="9" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="34" ht="14.25" customHeight="1">
-      <c r="A34" s="9">
-        <v>33.0</v>
-      </c>
-      <c r="C34" s="1" t="s">
-        <v>140</v>
-      </c>
-      <c r="D34" s="9" t="s">
-        <v>69</v>
-      </c>
-      <c r="E34" s="9" t="s">
-        <v>70</v>
-      </c>
-      <c r="F34" s="9" t="s">
-        <v>116</v>
-      </c>
-      <c r="G34" s="9" t="s">
-        <v>27</v>
-      </c>
-      <c r="H34" s="9" t="s">
-        <v>28</v>
-      </c>
-      <c r="I34" s="9" t="s">
-        <v>29</v>
-      </c>
-      <c r="J34" s="17" t="s">
-        <v>141</v>
-      </c>
-      <c r="K34" s="9" t="s">
-        <v>39</v>
-      </c>
-      <c r="L34" s="17">
-        <v>3.42881815E8</v>
-      </c>
-      <c r="M34" s="9" t="s">
-        <v>39</v>
-      </c>
-      <c r="N34" s="9" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="35" ht="14.25" customHeight="1">
-      <c r="A35" s="9">
-        <v>34.0</v>
-      </c>
-      <c r="C35" s="1" t="s">
-        <v>142</v>
-      </c>
-      <c r="D35" s="9" t="s">
-        <v>69</v>
-      </c>
-      <c r="E35" s="9" t="s">
-        <v>70</v>
-      </c>
-      <c r="F35" s="9" t="s">
-        <v>116</v>
-      </c>
-      <c r="G35" s="9" t="s">
-        <v>27</v>
-      </c>
-      <c r="H35" s="9" t="s">
-        <v>28</v>
-      </c>
-      <c r="I35" s="9" t="s">
-        <v>29</v>
-      </c>
-      <c r="J35" s="17" t="s">
-        <v>143</v>
-      </c>
-      <c r="K35" s="9" t="s">
-        <v>39</v>
-      </c>
-      <c r="L35" s="17">
-        <v>3.4322181E8</v>
-      </c>
-      <c r="M35" s="19" t="s">
-        <v>144</v>
-      </c>
-      <c r="N35" s="9" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="36" ht="14.25" customHeight="1">
-      <c r="A36" s="9">
-        <v>35.0</v>
-      </c>
-      <c r="C36" s="1" t="s">
-        <v>145</v>
-      </c>
-      <c r="D36" s="9" t="s">
-        <v>69</v>
-      </c>
-      <c r="E36" s="9" t="s">
-        <v>70</v>
-      </c>
-      <c r="F36" s="9" t="s">
-        <v>116</v>
-      </c>
-      <c r="G36" s="9" t="s">
-        <v>27</v>
-      </c>
-      <c r="H36" s="9" t="s">
-        <v>28</v>
-      </c>
-      <c r="I36" s="9" t="s">
-        <v>29</v>
-      </c>
-      <c r="J36" s="17" t="s">
-        <v>146</v>
-      </c>
-      <c r="K36" s="9" t="s">
-        <v>39</v>
-      </c>
-      <c r="L36" s="1" t="s">
-        <v>147</v>
-      </c>
-      <c r="M36" s="9" t="s">
-        <v>39</v>
-      </c>
-      <c r="N36" s="9" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="37" ht="14.25" customHeight="1">
-      <c r="A37" s="9">
-        <v>36.0</v>
-      </c>
-      <c r="C37" s="1" t="s">
-        <v>148</v>
-      </c>
-      <c r="D37" s="9" t="s">
-        <v>69</v>
-      </c>
-      <c r="E37" s="9" t="s">
-        <v>70</v>
-      </c>
-      <c r="F37" s="9" t="s">
-        <v>116</v>
-      </c>
-      <c r="G37" s="9" t="s">
-        <v>27</v>
-      </c>
-      <c r="H37" s="9" t="s">
-        <v>28</v>
-      </c>
-      <c r="I37" s="9" t="s">
-        <v>29</v>
-      </c>
-      <c r="J37" s="17" t="s">
-        <v>149</v>
-      </c>
-      <c r="K37" s="9" t="s">
-        <v>39</v>
-      </c>
-      <c r="L37" s="17">
-        <v>3.44488897E8</v>
-      </c>
-      <c r="M37" s="19" t="s">
-        <v>150</v>
-      </c>
-      <c r="N37" s="9" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="38" ht="14.25" customHeight="1">
-      <c r="A38" s="9">
-        <v>37.0</v>
-      </c>
-      <c r="C38" s="1" t="s">
-        <v>151</v>
-      </c>
-      <c r="D38" s="9" t="s">
-        <v>69</v>
-      </c>
-      <c r="E38" s="9" t="s">
-        <v>70</v>
-      </c>
-      <c r="F38" s="9" t="s">
-        <v>116</v>
-      </c>
-      <c r="G38" s="9" t="s">
-        <v>27</v>
-      </c>
-      <c r="H38" s="9" t="s">
-        <v>28</v>
-      </c>
-      <c r="I38" s="9" t="s">
-        <v>29</v>
-      </c>
-      <c r="J38" s="17" t="s">
-        <v>152</v>
-      </c>
-      <c r="K38" s="9" t="s">
-        <v>39</v>
-      </c>
-      <c r="L38" s="17">
-        <v>3.44447374E8</v>
-      </c>
-      <c r="M38" s="9" t="s">
-        <v>39</v>
-      </c>
-      <c r="N38" s="9" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="39" ht="14.25" customHeight="1">
-      <c r="A39" s="9">
-        <v>38.0</v>
-      </c>
-      <c r="C39" s="1" t="s">
-        <v>153</v>
-      </c>
-      <c r="D39" s="9" t="s">
-        <v>69</v>
-      </c>
-      <c r="E39" s="9" t="s">
-        <v>154</v>
-      </c>
-      <c r="F39" s="9" t="s">
-        <v>155</v>
-      </c>
-      <c r="G39" s="9" t="s">
-        <v>27</v>
-      </c>
-      <c r="H39" s="9" t="s">
-        <v>28</v>
-      </c>
-      <c r="I39" s="9" t="s">
-        <v>29</v>
-      </c>
-      <c r="J39" s="9" t="s">
-        <v>156</v>
-      </c>
-      <c r="K39" s="1" t="s">
-        <v>157</v>
-      </c>
-      <c r="L39" s="9" t="s">
-        <v>39</v>
-      </c>
-      <c r="M39" s="9" t="s">
-        <v>39</v>
-      </c>
-      <c r="N39" s="9" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="40" ht="14.25" customHeight="1">
-      <c r="A40" s="9">
-        <v>39.0</v>
-      </c>
-      <c r="C40" s="1" t="s">
-        <v>158</v>
-      </c>
-      <c r="D40" s="9" t="s">
-        <v>69</v>
-      </c>
-      <c r="E40" s="9" t="s">
-        <v>70</v>
-      </c>
-      <c r="F40" s="9" t="s">
-        <v>116</v>
-      </c>
-      <c r="G40" s="9" t="s">
-        <v>27</v>
-      </c>
-      <c r="H40" s="9" t="s">
-        <v>28</v>
-      </c>
-      <c r="I40" s="9" t="s">
-        <v>29</v>
-      </c>
-      <c r="J40" s="17" t="s">
-        <v>159</v>
-      </c>
-      <c r="K40" s="9" t="s">
-        <v>39</v>
-      </c>
-      <c r="L40" s="17">
-        <v>3.42888204E8</v>
-      </c>
-      <c r="M40" s="19" t="s">
-        <v>160</v>
-      </c>
-      <c r="N40" s="9" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="41" ht="14.25" customHeight="1">
-      <c r="A41" s="9">
-        <v>40.0</v>
-      </c>
-      <c r="C41" s="1" t="s">
-        <v>161</v>
-      </c>
-      <c r="D41" s="9" t="s">
-        <v>69</v>
-      </c>
-      <c r="E41" s="9" t="s">
-        <v>70</v>
-      </c>
-      <c r="F41" s="9" t="s">
-        <v>162</v>
-      </c>
-      <c r="G41" s="9" t="s">
-        <v>27</v>
-      </c>
-      <c r="H41" s="9" t="s">
-        <v>28</v>
-      </c>
-      <c r="I41" s="9" t="s">
-        <v>29</v>
-      </c>
-      <c r="J41" s="17" t="s">
-        <v>163</v>
-      </c>
-      <c r="K41" s="9" t="s">
-        <v>39</v>
-      </c>
-      <c r="L41" s="17">
-        <v>3.43015943E8</v>
-      </c>
-      <c r="M41" s="19" t="s">
-        <v>164</v>
-      </c>
-      <c r="N41" s="9" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="42" ht="14.25" customHeight="1">
-      <c r="A42" s="9">
-        <v>41.0</v>
-      </c>
-      <c r="C42" s="1" t="s">
-        <v>165</v>
-      </c>
-      <c r="D42" s="9" t="s">
-        <v>69</v>
-      </c>
-      <c r="E42" s="9" t="s">
-        <v>70</v>
-      </c>
-      <c r="F42" s="9" t="s">
-        <v>166</v>
-      </c>
-      <c r="G42" s="9" t="s">
-        <v>27</v>
-      </c>
-      <c r="H42" s="9" t="s">
-        <v>28</v>
-      </c>
-      <c r="I42" s="9" t="s">
-        <v>29</v>
-      </c>
-      <c r="J42" s="17" t="s">
-        <v>167</v>
-      </c>
-      <c r="K42" s="9" t="s">
-        <v>39</v>
-      </c>
-      <c r="L42" s="17">
-        <v>3.4288486E8</v>
-      </c>
-      <c r="M42" s="9" t="s">
-        <v>39</v>
-      </c>
-      <c r="N42" s="9" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="43" ht="14.25" customHeight="1">
-      <c r="A43" s="9">
-        <v>42.0</v>
-      </c>
-      <c r="C43" s="1" t="s">
-        <v>168</v>
-      </c>
-      <c r="D43" s="9" t="s">
-        <v>69</v>
-      </c>
-      <c r="E43" s="9" t="s">
-        <v>70</v>
-      </c>
-      <c r="F43" s="9" t="s">
-        <v>116</v>
-      </c>
-      <c r="G43" s="9" t="s">
-        <v>27</v>
-      </c>
-      <c r="H43" s="9" t="s">
-        <v>28</v>
-      </c>
-      <c r="I43" s="9" t="s">
-        <v>29</v>
-      </c>
-      <c r="J43" s="17" t="s">
-        <v>169</v>
-      </c>
-      <c r="K43" s="9" t="s">
-        <v>39</v>
-      </c>
-      <c r="L43" s="17">
-        <v>3.42884574E8</v>
-      </c>
-      <c r="M43" s="9" t="s">
-        <v>39</v>
-      </c>
-      <c r="N43" s="9" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="44" ht="14.25" customHeight="1">
-      <c r="A44" s="9">
-        <v>43.0</v>
-      </c>
-      <c r="C44" s="1" t="s">
-        <v>170</v>
-      </c>
-      <c r="D44" s="9" t="s">
-        <v>69</v>
-      </c>
-      <c r="E44" s="9" t="s">
-        <v>70</v>
-      </c>
-      <c r="F44" s="9" t="s">
-        <v>116</v>
-      </c>
-      <c r="G44" s="9" t="s">
-        <v>27</v>
-      </c>
-      <c r="H44" s="9" t="s">
-        <v>28</v>
-      </c>
-      <c r="I44" s="9" t="s">
-        <v>29</v>
-      </c>
-      <c r="J44" s="17" t="s">
-        <v>171</v>
-      </c>
-      <c r="K44" s="9" t="s">
-        <v>39</v>
-      </c>
-      <c r="L44" s="17">
-        <v>3.46129961E8</v>
-      </c>
-      <c r="M44" s="9" t="s">
-        <v>39</v>
-      </c>
-      <c r="N44" s="9" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="45" ht="14.25" customHeight="1">
-      <c r="A45" s="9">
-        <v>44.0</v>
-      </c>
-      <c r="C45" s="1" t="s">
-        <v>172</v>
-      </c>
-      <c r="D45" s="9" t="s">
-        <v>69</v>
-      </c>
-      <c r="E45" s="9" t="s">
-        <v>70</v>
-      </c>
-      <c r="F45" s="9" t="s">
-        <v>116</v>
-      </c>
-      <c r="G45" s="9" t="s">
-        <v>27</v>
-      </c>
-      <c r="H45" s="9" t="s">
-        <v>28</v>
-      </c>
-      <c r="I45" s="9" t="s">
-        <v>29</v>
-      </c>
-      <c r="J45" s="17" t="s">
-        <v>173</v>
-      </c>
-      <c r="K45" s="9" t="s">
-        <v>39</v>
-      </c>
-      <c r="L45" s="17">
-        <v>6.0460466E9</v>
-      </c>
-      <c r="M45" s="1" t="s">
-        <v>174</v>
-      </c>
-      <c r="N45" s="9" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="46" ht="14.25" customHeight="1">
-      <c r="A46" s="9">
-        <v>45.0</v>
-      </c>
-      <c r="C46" s="1" t="s">
-        <v>175</v>
-      </c>
-      <c r="D46" s="9" t="s">
-        <v>69</v>
-      </c>
-      <c r="E46" s="9" t="s">
-        <v>70</v>
-      </c>
-      <c r="F46" s="9" t="s">
-        <v>116</v>
-      </c>
-      <c r="G46" s="9" t="s">
-        <v>27</v>
-      </c>
-      <c r="H46" s="9" t="s">
-        <v>28</v>
-      </c>
-      <c r="I46" s="9" t="s">
-        <v>29</v>
-      </c>
-      <c r="J46" s="17" t="s">
-        <v>176</v>
-      </c>
-      <c r="K46" s="9" t="s">
-        <v>39</v>
-      </c>
-      <c r="L46" s="9" t="s">
-        <v>39</v>
-      </c>
-      <c r="M46" s="9" t="s">
-        <v>39</v>
-      </c>
-      <c r="N46" s="9" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="47" ht="14.25" customHeight="1">
-      <c r="A47" s="9">
-        <v>46.0</v>
-      </c>
-      <c r="C47" s="1" t="s">
-        <v>177</v>
-      </c>
-      <c r="D47" s="9" t="s">
-        <v>178</v>
-      </c>
-      <c r="E47" s="9" t="s">
-        <v>179</v>
-      </c>
-      <c r="F47" s="9" t="s">
-        <v>180</v>
-      </c>
-      <c r="G47" s="9" t="s">
-        <v>27</v>
-      </c>
-      <c r="H47" s="9" t="s">
-        <v>28</v>
-      </c>
-      <c r="I47" s="9" t="s">
-        <v>29</v>
-      </c>
-      <c r="J47" s="17" t="s">
-        <v>181</v>
-      </c>
-      <c r="K47" s="9" t="s">
-        <v>182</v>
-      </c>
-      <c r="L47" s="9" t="s">
-        <v>39</v>
-      </c>
-      <c r="M47" s="9" t="s">
-        <v>183</v>
-      </c>
-      <c r="N47" s="9" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="48" ht="14.25" customHeight="1">
-      <c r="A48" s="9">
-        <v>47.0</v>
-      </c>
-      <c r="C48" s="1" t="s">
-        <v>184</v>
-      </c>
-      <c r="D48" s="9" t="s">
-        <v>178</v>
-      </c>
-      <c r="E48" s="9" t="s">
-        <v>179</v>
-      </c>
-      <c r="F48" s="9" t="s">
-        <v>185</v>
-      </c>
-      <c r="G48" s="9" t="s">
-        <v>27</v>
-      </c>
-      <c r="H48" s="9" t="s">
-        <v>28</v>
-      </c>
-      <c r="I48" s="9" t="s">
-        <v>29</v>
-      </c>
-      <c r="J48" s="17" t="s">
-        <v>186</v>
-      </c>
-      <c r="K48" s="9" t="s">
-        <v>187</v>
-      </c>
-      <c r="L48" s="9" t="s">
-        <v>39</v>
-      </c>
-      <c r="M48" s="9" t="s">
-        <v>188</v>
-      </c>
-      <c r="N48" s="9" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="49" ht="14.25" customHeight="1">
-      <c r="A49" s="9">
-        <v>48.0</v>
-      </c>
-      <c r="C49" s="1" t="s">
-        <v>189</v>
-      </c>
-      <c r="D49" s="9" t="s">
-        <v>178</v>
-      </c>
-      <c r="E49" s="9" t="s">
-        <v>179</v>
-      </c>
-      <c r="F49" s="9" t="s">
-        <v>190</v>
-      </c>
-      <c r="G49" s="9" t="s">
-        <v>27</v>
-      </c>
-      <c r="H49" s="9" t="s">
-        <v>28</v>
-      </c>
-      <c r="I49" s="9" t="s">
-        <v>29</v>
-      </c>
-      <c r="J49" s="17" t="s">
-        <v>191</v>
-      </c>
-      <c r="K49" s="9" t="s">
-        <v>192</v>
-      </c>
-      <c r="L49" s="9" t="s">
-        <v>39</v>
-      </c>
-      <c r="M49" s="9" t="s">
-        <v>193</v>
-      </c>
-      <c r="N49" s="9" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="50" ht="14.25" customHeight="1">
-      <c r="A50" s="9">
-        <v>49.0</v>
-      </c>
-      <c r="C50" s="1" t="s">
-        <v>194</v>
-      </c>
-      <c r="D50" s="9" t="s">
-        <v>178</v>
-      </c>
-      <c r="E50" s="9" t="s">
-        <v>179</v>
-      </c>
-      <c r="F50" s="9" t="s">
-        <v>195</v>
-      </c>
-      <c r="G50" s="9" t="s">
-        <v>27</v>
-      </c>
-      <c r="H50" s="9" t="s">
-        <v>28</v>
-      </c>
-      <c r="I50" s="9" t="s">
-        <v>29</v>
-      </c>
-      <c r="J50" s="17" t="s">
-        <v>196</v>
-      </c>
-      <c r="K50" s="9" t="s">
-        <v>39</v>
-      </c>
-      <c r="L50" s="9" t="s">
-        <v>39</v>
-      </c>
-      <c r="M50" s="9" t="s">
-        <v>197</v>
-      </c>
-      <c r="N50" s="9" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="51" ht="14.25" customHeight="1">
-      <c r="A51" s="9">
-        <v>50.0</v>
-      </c>
-      <c r="C51" s="1" t="s">
-        <v>198</v>
-      </c>
-      <c r="D51" s="9" t="s">
-        <v>178</v>
-      </c>
-      <c r="E51" s="9" t="s">
-        <v>179</v>
-      </c>
-      <c r="F51" s="9" t="s">
-        <v>199</v>
-      </c>
-      <c r="G51" s="9" t="s">
-        <v>27</v>
-      </c>
-      <c r="H51" s="9" t="s">
-        <v>28</v>
-      </c>
-      <c r="I51" s="9" t="s">
-        <v>29</v>
-      </c>
-      <c r="J51" s="17" t="s">
-        <v>200</v>
-      </c>
-      <c r="K51" s="9" t="s">
-        <v>201</v>
-      </c>
-      <c r="L51" s="9" t="s">
-        <v>39</v>
-      </c>
-      <c r="M51" s="9" t="s">
-        <v>202</v>
-      </c>
-      <c r="N51" s="9" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="52" ht="14.25" customHeight="1">
-      <c r="A52" s="9">
-        <v>51.0</v>
-      </c>
-      <c r="C52" s="1" t="s">
-        <v>203</v>
-      </c>
-      <c r="D52" s="9" t="s">
-        <v>178</v>
-      </c>
-      <c r="E52" s="9" t="s">
-        <v>179</v>
-      </c>
-      <c r="F52" s="9" t="s">
-        <v>204</v>
-      </c>
-      <c r="G52" s="9" t="s">
-        <v>27</v>
-      </c>
-      <c r="H52" s="9" t="s">
-        <v>28</v>
-      </c>
-      <c r="I52" s="9" t="s">
-        <v>29</v>
-      </c>
-      <c r="K52" s="9" t="s">
-        <v>205</v>
-      </c>
-      <c r="L52" s="9" t="s">
-        <v>39</v>
-      </c>
-      <c r="M52" s="9" t="s">
-        <v>206</v>
-      </c>
-      <c r="N52" s="9" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="53" ht="14.25" customHeight="1">
-      <c r="A53" s="9">
-        <v>52.0</v>
-      </c>
-      <c r="C53" s="1" t="s">
-        <v>207</v>
-      </c>
-      <c r="D53" s="9" t="s">
-        <v>178</v>
-      </c>
-      <c r="E53" s="9" t="s">
-        <v>208</v>
-      </c>
-      <c r="F53" s="9" t="s">
-        <v>209</v>
-      </c>
-      <c r="G53" s="9" t="s">
-        <v>27</v>
-      </c>
-      <c r="H53" s="9" t="s">
-        <v>28</v>
-      </c>
-      <c r="I53" s="9" t="s">
-        <v>29</v>
-      </c>
-      <c r="J53" s="17" t="s">
-        <v>210</v>
-      </c>
-      <c r="K53" s="22">
-        <v>3.42880159E8</v>
-      </c>
-      <c r="L53" s="9" t="s">
-        <v>39</v>
-      </c>
-      <c r="M53" s="9" t="s">
-        <v>211</v>
-      </c>
-      <c r="N53" s="9" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="54" ht="14.25" customHeight="1">
-      <c r="A54" s="9">
-        <v>53.0</v>
-      </c>
-      <c r="C54" s="1" t="s">
-        <v>212</v>
-      </c>
-      <c r="D54" s="9" t="s">
-        <v>178</v>
-      </c>
-      <c r="E54" s="9" t="s">
-        <v>208</v>
-      </c>
-      <c r="F54" s="9" t="s">
-        <v>209</v>
-      </c>
-      <c r="G54" s="9" t="s">
-        <v>27</v>
-      </c>
-      <c r="H54" s="9" t="s">
-        <v>28</v>
-      </c>
-      <c r="I54" s="9" t="s">
-        <v>29</v>
-      </c>
-      <c r="J54" s="17" t="s">
-        <v>213</v>
-      </c>
-      <c r="K54" s="22">
-        <v>3.045383728E9</v>
-      </c>
-      <c r="L54" s="9" t="s">
-        <v>39</v>
-      </c>
-      <c r="M54" s="9" t="s">
-        <v>214</v>
-      </c>
-      <c r="N54" s="9" t="s">
-        <v>215</v>
-      </c>
-    </row>
-    <row r="55" ht="14.25" customHeight="1">
-      <c r="A55" s="9">
-        <v>54.0</v>
-      </c>
-      <c r="C55" s="1" t="s">
-        <v>216</v>
-      </c>
-      <c r="D55" s="9" t="s">
-        <v>178</v>
-      </c>
-      <c r="E55" s="9" t="s">
-        <v>208</v>
-      </c>
-      <c r="F55" s="9" t="s">
-        <v>209</v>
-      </c>
-      <c r="G55" s="9" t="s">
-        <v>27</v>
-      </c>
-      <c r="H55" s="9" t="s">
-        <v>28</v>
-      </c>
-      <c r="I55" s="9" t="s">
-        <v>29</v>
-      </c>
-      <c r="J55" s="9" t="s">
-        <v>217</v>
-      </c>
-      <c r="K55" s="22">
-        <v>3.002730515E9</v>
-      </c>
-      <c r="L55" s="9" t="s">
-        <v>39</v>
-      </c>
-      <c r="M55" s="9" t="s">
-        <v>218</v>
-      </c>
-      <c r="N55" s="23" t="s">
-        <v>219</v>
-      </c>
-    </row>
-    <row r="56" ht="14.25" customHeight="1">
-      <c r="A56" s="9">
-        <v>55.0</v>
-      </c>
-      <c r="C56" s="1" t="s">
-        <v>220</v>
-      </c>
-      <c r="D56" s="9" t="s">
-        <v>178</v>
-      </c>
-      <c r="E56" s="9" t="s">
-        <v>208</v>
-      </c>
-      <c r="F56" s="9" t="s">
-        <v>209</v>
-      </c>
-      <c r="G56" s="9" t="s">
-        <v>27</v>
-      </c>
-      <c r="H56" s="9" t="s">
-        <v>28</v>
-      </c>
-      <c r="I56" s="9" t="s">
-        <v>29</v>
-      </c>
-      <c r="J56" s="17" t="s">
-        <v>221</v>
-      </c>
-      <c r="K56" s="22">
-        <v>3.022705056E9</v>
-      </c>
-      <c r="L56" s="9" t="s">
-        <v>39</v>
-      </c>
-      <c r="M56" s="9" t="s">
-        <v>222</v>
-      </c>
-      <c r="N56" s="23" t="s">
-        <v>223</v>
-      </c>
-    </row>
-    <row r="57" ht="14.25" customHeight="1">
-      <c r="A57" s="9">
-        <v>56.0</v>
-      </c>
-      <c r="C57" s="1" t="s">
-        <v>224</v>
-      </c>
-      <c r="D57" s="9" t="s">
-        <v>178</v>
-      </c>
-      <c r="E57" s="9" t="s">
-        <v>208</v>
-      </c>
-      <c r="F57" s="9" t="s">
-        <v>209</v>
-      </c>
-      <c r="G57" s="9" t="s">
-        <v>27</v>
-      </c>
-      <c r="H57" s="9" t="s">
-        <v>28</v>
-      </c>
-      <c r="I57" s="9" t="s">
-        <v>29</v>
-      </c>
-      <c r="J57" s="17" t="s">
-        <v>225</v>
-      </c>
-      <c r="K57" s="22">
-        <v>3.003568587E9</v>
-      </c>
-      <c r="L57" s="9" t="s">
-        <v>39</v>
-      </c>
-      <c r="M57" s="9" t="s">
-        <v>226</v>
-      </c>
-      <c r="N57" s="9" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="58" ht="14.25" customHeight="1">
-      <c r="A58" s="9">
-        <v>57.0</v>
-      </c>
-      <c r="C58" s="1" t="s">
-        <v>227</v>
-      </c>
-      <c r="D58" s="9" t="s">
-        <v>178</v>
-      </c>
-      <c r="E58" s="9" t="s">
-        <v>208</v>
-      </c>
-      <c r="F58" s="9" t="s">
-        <v>209</v>
-      </c>
-      <c r="G58" s="9" t="s">
-        <v>27</v>
-      </c>
-      <c r="H58" s="9" t="s">
-        <v>28</v>
-      </c>
-      <c r="I58" s="9" t="s">
-        <v>29</v>
-      </c>
-      <c r="J58" s="17" t="s">
-        <v>228</v>
-      </c>
-      <c r="K58" s="22" t="s">
-        <v>39</v>
-      </c>
-      <c r="L58" s="22">
-        <v>3.43665019E8</v>
-      </c>
-      <c r="M58" s="9" t="s">
-        <v>229</v>
-      </c>
-      <c r="N58" s="9" t="s">
-        <v>230</v>
-      </c>
-    </row>
-    <row r="59" ht="14.25" customHeight="1">
-      <c r="A59" s="9">
-        <v>58.0</v>
-      </c>
-      <c r="C59" s="1" t="s">
-        <v>231</v>
-      </c>
-      <c r="D59" s="9" t="s">
-        <v>178</v>
-      </c>
-      <c r="E59" s="9" t="s">
-        <v>208</v>
-      </c>
-      <c r="F59" s="9" t="s">
-        <v>209</v>
-      </c>
-      <c r="G59" s="9" t="s">
-        <v>27</v>
-      </c>
-      <c r="H59" s="9" t="s">
-        <v>28</v>
-      </c>
-      <c r="I59" s="9" t="s">
-        <v>29</v>
-      </c>
-      <c r="J59" s="17" t="s">
-        <v>232</v>
-      </c>
-      <c r="K59" s="22" t="s">
-        <v>39</v>
-      </c>
-      <c r="L59" s="9" t="s">
-        <v>39</v>
-      </c>
-      <c r="M59" s="9" t="s">
-        <v>233</v>
-      </c>
-      <c r="N59" s="9" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="60" ht="14.25" customHeight="1">
-      <c r="A60" s="9">
-        <v>59.0</v>
-      </c>
-      <c r="C60" s="1" t="s">
+      <c r="D62" t="s">
         <v>234</v>
       </c>
-      <c r="D60" s="9" t="s">
-        <v>178</v>
-      </c>
-      <c r="E60" s="9" t="s">
-        <v>208</v>
-      </c>
-      <c r="F60" s="9" t="s">
-        <v>209</v>
-      </c>
-      <c r="G60" s="9" t="s">
-        <v>27</v>
-      </c>
-      <c r="H60" s="9" t="s">
-        <v>28</v>
-      </c>
-      <c r="I60" s="9" t="s">
-        <v>29</v>
-      </c>
-      <c r="J60" s="17" t="s">
+      <c r="E62" t="s">
         <v>235</v>
       </c>
-      <c r="K60" s="22">
-        <v>3.43660313E8</v>
-      </c>
-      <c r="L60" s="9" t="s">
-        <v>39</v>
-      </c>
-      <c r="M60" s="9" t="s">
+      <c r="F62" t="s">
         <v>236</v>
       </c>
-      <c r="N60" s="9" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="61" ht="14.25" customHeight="1">
-      <c r="A61" s="9">
-        <v>60.0</v>
-      </c>
-      <c r="C61" s="1" t="s">
+      <c r="G62" t="s">
         <v>237</v>
       </c>
-      <c r="D61" s="9" t="s">
-        <v>178</v>
-      </c>
-      <c r="E61" s="9" t="s">
-        <v>208</v>
-      </c>
-      <c r="F61" s="9" t="s">
-        <v>209</v>
-      </c>
-      <c r="G61" s="9" t="s">
-        <v>27</v>
-      </c>
-      <c r="H61" s="9" t="s">
-        <v>28</v>
-      </c>
-      <c r="I61" s="9" t="s">
-        <v>29</v>
-      </c>
-      <c r="J61" s="17" t="s">
+      <c r="H62" t="s">
         <v>238</v>
       </c>
-      <c r="K61" s="22">
-        <v>3.003455457E9</v>
-      </c>
-      <c r="L61" s="9" t="s">
-        <v>39</v>
-      </c>
-      <c r="M61" s="9" t="s">
+      <c r="I62" t="s">
+        <v>41</v>
+      </c>
+      <c r="J62" t="s">
         <v>239</v>
       </c>
-      <c r="N61" s="9" t="s">
+      <c r="M62" t="s">
         <v>240</v>
       </c>
     </row>
-    <row r="62" ht="14.25" customHeight="1">
-      <c r="A62" s="9">
-        <v>61.0</v>
-      </c>
-      <c r="C62" s="1" t="s">
+    <row r="63" spans="2:13" ht="14.25" customHeight="1">
+      <c r="B63" t="s">
         <v>241</v>
       </c>
-      <c r="D62" s="9" t="s">
-        <v>178</v>
-      </c>
-      <c r="E62" s="9" t="s">
-        <v>208</v>
-      </c>
-      <c r="F62" s="9" t="s">
-        <v>209</v>
-      </c>
-      <c r="G62" s="9" t="s">
-        <v>27</v>
-      </c>
-      <c r="H62" s="9" t="s">
-        <v>28</v>
-      </c>
-      <c r="I62" s="9" t="s">
-        <v>29</v>
-      </c>
-      <c r="J62" s="17" t="s">
+      <c r="C63" t="s">
+        <v>96</v>
+      </c>
+      <c r="D63" t="s">
+        <v>234</v>
+      </c>
+      <c r="E63" t="s">
         <v>242</v>
       </c>
-      <c r="K62" s="22">
-        <v>3.185108864E9</v>
-      </c>
-      <c r="L62" s="9" t="s">
-        <v>39</v>
-      </c>
-      <c r="M62" s="9" t="s">
+      <c r="F63" t="s">
+        <v>236</v>
+      </c>
+      <c r="G63" t="s">
+        <v>237</v>
+      </c>
+      <c r="H63" t="s">
+        <v>238</v>
+      </c>
+      <c r="I63" t="s">
+        <v>41</v>
+      </c>
+      <c r="J63" t="s">
+        <v>239</v>
+      </c>
+      <c r="M63" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="64" spans="2:13" ht="14.25" customHeight="1">
+      <c r="B64" t="s">
         <v>243</v>
       </c>
-      <c r="N62" s="9" t="s">
+      <c r="C64" t="s">
         <v>244</v>
       </c>
-    </row>
-    <row r="63" ht="14.25" customHeight="1">
-      <c r="A63" s="9">
-        <v>62.0</v>
-      </c>
-    </row>
-    <row r="64" ht="14.25" customHeight="1">
-      <c r="A64" s="9">
-        <v>63.0</v>
-      </c>
-    </row>
-    <row r="65" ht="14.25" customHeight="1">
-      <c r="A65" s="9">
-        <v>64.0</v>
-      </c>
-    </row>
-    <row r="66" ht="14.25" customHeight="1">
-      <c r="A66" s="9">
-        <v>65.0</v>
-      </c>
-    </row>
-    <row r="67" ht="14.25" customHeight="1"/>
-    <row r="68" ht="14.25" customHeight="1"/>
-    <row r="69" ht="14.25" customHeight="1"/>
-    <row r="70" ht="14.25" customHeight="1"/>
-    <row r="71" ht="14.25" customHeight="1"/>
-    <row r="72" ht="14.25" customHeight="1"/>
-    <row r="73" ht="14.25" customHeight="1"/>
-    <row r="74" ht="14.25" customHeight="1"/>
-    <row r="75" ht="14.25" customHeight="1"/>
-    <row r="76" ht="14.25" customHeight="1"/>
-    <row r="77" ht="14.25" customHeight="1"/>
-    <row r="78" ht="14.25" customHeight="1"/>
-    <row r="79" ht="14.25" customHeight="1"/>
-    <row r="80" ht="14.25" customHeight="1"/>
+      <c r="D64" t="s">
+        <v>245</v>
+      </c>
+      <c r="E64" t="s">
+        <v>244</v>
+      </c>
+      <c r="F64" t="s">
+        <v>236</v>
+      </c>
+      <c r="G64" t="s">
+        <v>237</v>
+      </c>
+      <c r="H64" t="s">
+        <v>238</v>
+      </c>
+      <c r="I64" t="s">
+        <v>246</v>
+      </c>
+    </row>
+    <row r="65" spans="2:9" ht="14.25" customHeight="1">
+      <c r="B65" t="s">
+        <v>243</v>
+      </c>
+      <c r="C65" t="s">
+        <v>244</v>
+      </c>
+      <c r="D65" t="s">
+        <v>245</v>
+      </c>
+      <c r="E65" t="s">
+        <v>244</v>
+      </c>
+      <c r="F65" t="s">
+        <v>236</v>
+      </c>
+      <c r="G65" t="s">
+        <v>237</v>
+      </c>
+      <c r="H65" t="s">
+        <v>238</v>
+      </c>
+      <c r="I65" t="s">
+        <v>246</v>
+      </c>
+    </row>
+    <row r="66" spans="2:9" ht="14.25" customHeight="1">
+      <c r="B66" t="s">
+        <v>243</v>
+      </c>
+      <c r="C66" t="s">
+        <v>244</v>
+      </c>
+      <c r="D66" t="s">
+        <v>245</v>
+      </c>
+      <c r="E66" t="s">
+        <v>244</v>
+      </c>
+      <c r="F66" t="s">
+        <v>236</v>
+      </c>
+      <c r="G66" t="s">
+        <v>237</v>
+      </c>
+      <c r="H66" t="s">
+        <v>238</v>
+      </c>
+      <c r="I66" t="s">
+        <v>246</v>
+      </c>
+    </row>
+    <row r="67" spans="2:9" ht="14.25" customHeight="1">
+      <c r="B67" t="s">
+        <v>243</v>
+      </c>
+      <c r="C67" t="s">
+        <v>244</v>
+      </c>
+      <c r="D67" t="s">
+        <v>245</v>
+      </c>
+      <c r="E67" t="s">
+        <v>244</v>
+      </c>
+      <c r="F67" t="s">
+        <v>236</v>
+      </c>
+      <c r="G67" t="s">
+        <v>237</v>
+      </c>
+      <c r="H67" t="s">
+        <v>238</v>
+      </c>
+      <c r="I67" t="s">
+        <v>246</v>
+      </c>
+    </row>
+    <row r="68" spans="2:9" ht="14.25" customHeight="1"/>
+    <row r="69" spans="2:9" ht="14.25" customHeight="1"/>
+    <row r="70" spans="2:9" ht="14.25" customHeight="1"/>
+    <row r="71" spans="2:9" ht="14.25" customHeight="1"/>
+    <row r="72" spans="2:9" ht="14.25" customHeight="1"/>
+    <row r="73" spans="2:9" ht="14.25" customHeight="1"/>
+    <row r="74" spans="2:9" ht="14.25" customHeight="1"/>
+    <row r="75" spans="2:9" ht="14.25" customHeight="1"/>
+    <row r="76" spans="2:9" ht="14.25" customHeight="1"/>
+    <row r="77" spans="2:9" ht="14.25" customHeight="1"/>
+    <row r="78" spans="2:9" ht="14.25" customHeight="1"/>
+    <row r="79" spans="2:9" ht="14.25" customHeight="1"/>
+    <row r="80" spans="2:9" ht="14.25" customHeight="1"/>
     <row r="81" ht="14.25" customHeight="1"/>
     <row r="82" ht="14.25" customHeight="1"/>
     <row r="83" ht="14.25" customHeight="1"/>
@@ -5776,85 +5673,74 @@
     <row r="991" ht="14.25" customHeight="1"/>
     <row r="992" ht="14.25" customHeight="1"/>
     <row r="993" ht="14.25" customHeight="1"/>
-    <row r="994" ht="14.25" customHeight="1"/>
-    <row r="995" ht="14.25" customHeight="1"/>
-    <row r="996" ht="14.25" customHeight="1"/>
-    <row r="997" ht="14.25" customHeight="1"/>
-    <row r="998" ht="14.25" customHeight="1"/>
-    <row r="999" ht="14.25" customHeight="1"/>
-    <row r="1000" ht="14.25" customHeight="1"/>
   </sheetData>
   <hyperlinks>
-    <hyperlink r:id="rId2" ref="M3"/>
-    <hyperlink r:id="rId3" ref="M5"/>
-    <hyperlink r:id="rId4" ref="N5"/>
-    <hyperlink r:id="rId5" ref="M21"/>
-    <hyperlink r:id="rId6" ref="M22"/>
-    <hyperlink r:id="rId7" ref="N22"/>
-    <hyperlink r:id="rId8" ref="M24"/>
-    <hyperlink r:id="rId9" ref="M25"/>
-    <hyperlink r:id="rId10" ref="M35"/>
-    <hyperlink r:id="rId11" ref="M37"/>
-    <hyperlink r:id="rId12" ref="M40"/>
-    <hyperlink r:id="rId13" ref="M41"/>
-    <hyperlink r:id="rId14" ref="N55"/>
-    <hyperlink r:id="rId15" ref="N56"/>
+    <hyperlink ref="L2" r:id="rId1" xr:uid="{00000000-0004-0000-0100-000000000000}"/>
+    <hyperlink ref="L4" r:id="rId2" xr:uid="{00000000-0004-0000-0100-000001000000}"/>
+    <hyperlink ref="M4" r:id="rId3" xr:uid="{00000000-0004-0000-0100-000002000000}"/>
+    <hyperlink ref="L20" r:id="rId4" xr:uid="{00000000-0004-0000-0100-000003000000}"/>
+    <hyperlink ref="L21" r:id="rId5" xr:uid="{00000000-0004-0000-0100-000004000000}"/>
+    <hyperlink ref="M21" r:id="rId6" xr:uid="{00000000-0004-0000-0100-000005000000}"/>
+    <hyperlink ref="L23" r:id="rId7" xr:uid="{00000000-0004-0000-0100-000006000000}"/>
+    <hyperlink ref="L24" r:id="rId8" xr:uid="{00000000-0004-0000-0100-000007000000}"/>
+    <hyperlink ref="L34" r:id="rId9" xr:uid="{00000000-0004-0000-0100-000008000000}"/>
+    <hyperlink ref="L36" r:id="rId10" xr:uid="{00000000-0004-0000-0100-000009000000}"/>
+    <hyperlink ref="L39" r:id="rId11" xr:uid="{00000000-0004-0000-0100-00000A000000}"/>
+    <hyperlink ref="L40" r:id="rId12" xr:uid="{00000000-0004-0000-0100-00000B000000}"/>
+    <hyperlink ref="M54" r:id="rId13" xr:uid="{00000000-0004-0000-0100-00000C000000}"/>
+    <hyperlink ref="M55" r:id="rId14" xr:uid="{00000000-0004-0000-0100-00000D000000}"/>
   </hyperlinks>
-  <printOptions/>
-  <pageMargins bottom="0.75" footer="0.0" header="0.0" left="0.7" right="0.7" top="0.75"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
   <pageSetup orientation="landscape"/>
-  <drawing r:id="rId16"/>
-  <legacyDrawing r:id="rId17"/>
+  <legacyDrawing r:id="rId15"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-  <sheetPr>
-    <pageSetUpPr/>
-  </sheetPr>
-  <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.0"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
+  <dimension ref="B1:C1000"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="12.59765625" defaultRowHeight="15" customHeight="1"/>
   <cols>
-    <col customWidth="1" min="1" max="26" width="10.63"/>
+    <col min="1" max="26" width="10.59765625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="14.25" customHeight="1"/>
-    <row r="2" ht="14.25" customHeight="1">
+    <row r="1" spans="2:3" ht="14.25" customHeight="1"/>
+    <row r="2" spans="2:3" ht="14.25" customHeight="1">
       <c r="B2" s="1" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>246</v>
-      </c>
-    </row>
-    <row r="3" ht="14.25" customHeight="1">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="3" spans="2:3" ht="14.25" customHeight="1">
       <c r="B3" s="1" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>248</v>
-      </c>
-    </row>
-    <row r="4" ht="14.25" customHeight="1">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="4" spans="2:3" ht="14.25" customHeight="1">
       <c r="B4" s="1" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>249</v>
-      </c>
-    </row>
-    <row r="5" ht="14.25" customHeight="1"/>
-    <row r="6" ht="14.25" customHeight="1"/>
-    <row r="7" ht="14.25" customHeight="1"/>
-    <row r="8" ht="14.25" customHeight="1"/>
-    <row r="9" ht="14.25" customHeight="1"/>
-    <row r="10" ht="14.25" customHeight="1"/>
-    <row r="11" ht="14.25" customHeight="1"/>
-    <row r="12" ht="14.25" customHeight="1"/>
-    <row r="13" ht="14.25" customHeight="1"/>
-    <row r="14" ht="14.25" customHeight="1"/>
-    <row r="15" ht="14.25" customHeight="1"/>
-    <row r="16" ht="14.25" customHeight="1"/>
+        <v>251</v>
+      </c>
+    </row>
+    <row r="5" spans="2:3" ht="14.25" customHeight="1"/>
+    <row r="6" spans="2:3" ht="14.25" customHeight="1"/>
+    <row r="7" spans="2:3" ht="14.25" customHeight="1"/>
+    <row r="8" spans="2:3" ht="14.25" customHeight="1"/>
+    <row r="9" spans="2:3" ht="14.25" customHeight="1"/>
+    <row r="10" spans="2:3" ht="14.25" customHeight="1"/>
+    <row r="11" spans="2:3" ht="14.25" customHeight="1"/>
+    <row r="12" spans="2:3" ht="14.25" customHeight="1"/>
+    <row r="13" spans="2:3" ht="14.25" customHeight="1"/>
+    <row r="14" spans="2:3" ht="14.25" customHeight="1"/>
+    <row r="15" spans="2:3" ht="14.25" customHeight="1"/>
+    <row r="16" spans="2:3" ht="14.25" customHeight="1"/>
     <row r="17" ht="14.25" customHeight="1"/>
     <row r="18" ht="14.25" customHeight="1"/>
     <row r="19" ht="14.25" customHeight="1"/>
@@ -6840,9 +6726,7 @@
     <row r="999" ht="14.25" customHeight="1"/>
     <row r="1000" ht="14.25" customHeight="1"/>
   </sheetData>
-  <printOptions/>
-  <pageMargins bottom="0.75" footer="0.0" header="0.0" left="0.7" right="0.7" top="0.75"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
   <pageSetup orientation="landscape"/>
-  <drawing r:id="rId1"/>
 </worksheet>
 </file>
--- a/recomendador_sabaneta/data/base_actualizada.xlsx
+++ b/recomendador_sabaneta/data/base_actualizada.xlsx
@@ -37,14 +37,14 @@
   </commentList>
   <extLst>
     <ext uri="GoogleSheetsCustomDataVersion2">
-      <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" r:id="rId1" roundtripDataSignature="AMtx7mhzufvoaGk4DuuCXa87oo9Z+Fm/zw=="/>
+      <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" r:id="rId1" roundtripDataSignature="AMtx7mig0PM/i++D6oLh/q/dfvryoRjZGw=="/>
     </ext>
   </extLst>
 </comments>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1059" uniqueCount="363">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1157" uniqueCount="405">
   <si>
     <t>Introducción teorica sobre el ciclo de vida de proyecto de ML</t>
   </si>
@@ -1120,6 +1120,132 @@
     <t>Calle 72 Sur # 44-05</t>
   </si>
   <si>
+    <t>La Colmena sur</t>
+  </si>
+  <si>
+    <t>Ferretero</t>
+  </si>
+  <si>
+    <t>Todo en llaves de seguridad</t>
+  </si>
+  <si>
+    <t>Carrera 45 # 72 Sur-35</t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/cafemilagrooficial/</t>
+  </si>
+  <si>
+    <t>Jvan Londoño</t>
+  </si>
+  <si>
+    <t>Publicitario</t>
+  </si>
+  <si>
+    <t>Fotografía</t>
+  </si>
+  <si>
+    <t>Fotografía, retratos, publicidad</t>
+  </si>
+  <si>
+    <t>Calle 72 Sur #45 A-60</t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/jvan.londono.studio/</t>
+  </si>
+  <si>
+    <t>Guillego Estudio Fotográfico</t>
+  </si>
+  <si>
+    <t>Servicio fotografico, eventos sociales, diseño e impresión</t>
+  </si>
+  <si>
+    <t>Calle 72 Sur # 45 A -09</t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/gestudiofotografico/?hl=es</t>
+  </si>
+  <si>
+    <t>La Vaca Lola</t>
+  </si>
+  <si>
+    <t>Retail</t>
+  </si>
+  <si>
+    <t>Comercio Minorista</t>
+  </si>
+  <si>
+    <t>Productos para bebe</t>
+  </si>
+  <si>
+    <t>Carrera 47 # 75 Sur 16</t>
+  </si>
+  <si>
+    <t>https://www.facebook.com/p/La-vaca-Lola-Tienda-para-Pekes-100062939305948/</t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/lavacalolatiendaparapekes/?hl=es-la</t>
+  </si>
+  <si>
+    <t>Rocky Cueros</t>
+  </si>
+  <si>
+    <t>Venta accesorios para montar caballo, monturas, alfombras,frenos, riendas, aperos</t>
+  </si>
+  <si>
+    <t>Calle 72 Sur # 45A-10</t>
+  </si>
+  <si>
+    <t>https://www.facebook.com/rockycueross/?locale=es_LA</t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/rockycueros/</t>
+  </si>
+  <si>
+    <t>Sastreria DYD</t>
+  </si>
+  <si>
+    <t>Calle 69 Sur # 46-27</t>
+  </si>
+  <si>
+    <t>https://www.facebook.com/sastrw/?locale=es_LA</t>
+  </si>
+  <si>
+    <t>Colombia	Antioquia	Sabaneta</t>
+  </si>
+  <si>
+    <t>Empeliculados</t>
+  </si>
+  <si>
+    <t>Tienda de articulos de colección</t>
+  </si>
+  <si>
+    <t>Carrera 48 # 76D Sur 52</t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/empeliculadoscol/</t>
+  </si>
+  <si>
+    <t>Tienda de Regalos Sabaneta</t>
+  </si>
+  <si>
+    <t>Anchetas, desayunos sorpresa, empaques para regalo, cajas y accesorios</t>
+  </si>
+  <si>
+    <t>Calle 72 Sur #46-37</t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/tiendaderegalossabaneta/?hl=es</t>
+  </si>
+  <si>
+    <t>Proyecto y Enfoque Inmobiliario</t>
+  </si>
+  <si>
+    <t>Cl 66 S # 43C-84</t>
+  </si>
+  <si>
+    <t>https://www.facebook.com/p/Proyecto-Y-Enfoque-Inmobiliario-100083624130170/</t>
+  </si>
+  <si>
     <t>MV</t>
   </si>
   <si>
@@ -1139,7 +1265,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <fonts count="9">
+  <fonts count="10">
     <font>
       <sz val="11.0"/>
       <color theme="1"/>
@@ -1190,6 +1316,12 @@
       <color theme="1"/>
       <name val="Arial"/>
     </font>
+    <font>
+      <u/>
+      <sz val="11.0"/>
+      <color rgb="FF000000"/>
+      <name val="Arial"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -1205,7 +1337,7 @@
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="13">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
@@ -1234,6 +1366,9 @@
       <alignment readingOrder="0"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="8" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment readingOrder="0"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="9" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0"/>
     </xf>
   </cellXfs>
@@ -14249,18 +14384,42 @@
     </row>
     <row r="93" ht="14.25" customHeight="1">
       <c r="A93" s="1"/>
-      <c r="B93" s="1"/>
-      <c r="C93" s="1"/>
-      <c r="D93" s="1"/>
-      <c r="E93" s="1"/>
-      <c r="F93" s="1"/>
-      <c r="G93" s="1"/>
-      <c r="H93" s="1"/>
-      <c r="I93" s="1"/>
-      <c r="J93" s="1"/>
-      <c r="K93" s="1"/>
-      <c r="L93" s="1"/>
-      <c r="M93" s="1"/>
+      <c r="B93" s="8" t="s">
+        <v>358</v>
+      </c>
+      <c r="C93" s="8" t="s">
+        <v>359</v>
+      </c>
+      <c r="D93" s="8" t="s">
+        <v>359</v>
+      </c>
+      <c r="E93" s="8" t="s">
+        <v>360</v>
+      </c>
+      <c r="F93" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="G93" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="H93" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="I93" s="8" t="s">
+        <v>361</v>
+      </c>
+      <c r="J93" s="8">
+        <v>3.155434962E9</v>
+      </c>
+      <c r="K93" s="8" t="s">
+        <v>30</v>
+      </c>
+      <c r="L93" s="8" t="s">
+        <v>30</v>
+      </c>
+      <c r="M93" s="12" t="s">
+        <v>362</v>
+      </c>
       <c r="N93" s="1"/>
       <c r="O93" s="1"/>
       <c r="P93" s="1"/>
@@ -14275,18 +14434,42 @@
     </row>
     <row r="94" ht="14.25" customHeight="1">
       <c r="A94" s="1"/>
-      <c r="B94" s="1"/>
-      <c r="C94" s="1"/>
-      <c r="D94" s="1"/>
-      <c r="E94" s="1"/>
-      <c r="F94" s="1"/>
-      <c r="G94" s="1"/>
-      <c r="H94" s="1"/>
-      <c r="I94" s="1"/>
-      <c r="J94" s="1"/>
-      <c r="K94" s="1"/>
-      <c r="L94" s="1"/>
-      <c r="M94" s="1"/>
+      <c r="B94" s="8" t="s">
+        <v>363</v>
+      </c>
+      <c r="C94" s="8" t="s">
+        <v>364</v>
+      </c>
+      <c r="D94" s="8" t="s">
+        <v>365</v>
+      </c>
+      <c r="E94" s="8" t="s">
+        <v>366</v>
+      </c>
+      <c r="F94" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="G94" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="H94" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="I94" s="8" t="s">
+        <v>367</v>
+      </c>
+      <c r="J94" s="8">
+        <v>3.218714789E9</v>
+      </c>
+      <c r="K94" s="8" t="s">
+        <v>30</v>
+      </c>
+      <c r="L94" s="8" t="s">
+        <v>30</v>
+      </c>
+      <c r="M94" s="10" t="s">
+        <v>368</v>
+      </c>
       <c r="N94" s="1"/>
       <c r="O94" s="1"/>
       <c r="P94" s="1"/>
@@ -14301,18 +14484,42 @@
     </row>
     <row r="95" ht="14.25" customHeight="1">
       <c r="A95" s="1"/>
-      <c r="B95" s="1"/>
-      <c r="C95" s="1"/>
-      <c r="D95" s="1"/>
-      <c r="E95" s="1"/>
-      <c r="F95" s="1"/>
-      <c r="G95" s="1"/>
-      <c r="H95" s="1"/>
-      <c r="I95" s="1"/>
-      <c r="J95" s="1"/>
-      <c r="K95" s="1"/>
-      <c r="L95" s="1"/>
-      <c r="M95" s="1"/>
+      <c r="B95" s="8" t="s">
+        <v>369</v>
+      </c>
+      <c r="C95" s="8" t="s">
+        <v>364</v>
+      </c>
+      <c r="D95" s="8" t="s">
+        <v>365</v>
+      </c>
+      <c r="E95" s="8" t="s">
+        <v>370</v>
+      </c>
+      <c r="F95" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="G95" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="H95" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="I95" s="8" t="s">
+        <v>371</v>
+      </c>
+      <c r="J95" s="8">
+        <v>3.218054649E9</v>
+      </c>
+      <c r="K95" s="8" t="s">
+        <v>30</v>
+      </c>
+      <c r="L95" s="8" t="s">
+        <v>30</v>
+      </c>
+      <c r="M95" s="12" t="s">
+        <v>372</v>
+      </c>
       <c r="N95" s="1"/>
       <c r="O95" s="1"/>
       <c r="P95" s="1"/>
@@ -14327,18 +14534,42 @@
     </row>
     <row r="96" ht="14.25" customHeight="1">
       <c r="A96" s="1"/>
-      <c r="B96" s="1"/>
-      <c r="C96" s="1"/>
-      <c r="D96" s="1"/>
-      <c r="E96" s="1"/>
-      <c r="F96" s="1"/>
-      <c r="G96" s="1"/>
-      <c r="H96" s="1"/>
-      <c r="I96" s="1"/>
-      <c r="J96" s="1"/>
-      <c r="K96" s="1"/>
-      <c r="L96" s="1"/>
-      <c r="M96" s="1"/>
+      <c r="B96" s="8" t="s">
+        <v>373</v>
+      </c>
+      <c r="C96" s="8" t="s">
+        <v>374</v>
+      </c>
+      <c r="D96" s="8" t="s">
+        <v>375</v>
+      </c>
+      <c r="E96" s="8" t="s">
+        <v>376</v>
+      </c>
+      <c r="F96" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="G96" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="H96" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="I96" s="8" t="s">
+        <v>377</v>
+      </c>
+      <c r="J96" s="8">
+        <v>3.006760642E9</v>
+      </c>
+      <c r="K96" s="8" t="s">
+        <v>30</v>
+      </c>
+      <c r="L96" s="10" t="s">
+        <v>378</v>
+      </c>
+      <c r="M96" s="11" t="s">
+        <v>379</v>
+      </c>
       <c r="N96" s="1"/>
       <c r="O96" s="1"/>
       <c r="P96" s="1"/>
@@ -14353,18 +14584,42 @@
     </row>
     <row r="97" ht="14.25" customHeight="1">
       <c r="A97" s="1"/>
-      <c r="B97" s="1"/>
-      <c r="C97" s="1"/>
-      <c r="D97" s="1"/>
-      <c r="E97" s="1"/>
-      <c r="F97" s="1"/>
-      <c r="G97" s="1"/>
-      <c r="H97" s="1"/>
-      <c r="I97" s="1"/>
-      <c r="J97" s="1"/>
-      <c r="K97" s="1"/>
-      <c r="L97" s="1"/>
-      <c r="M97" s="1"/>
+      <c r="B97" s="8" t="s">
+        <v>380</v>
+      </c>
+      <c r="C97" s="8" t="s">
+        <v>374</v>
+      </c>
+      <c r="D97" s="8" t="s">
+        <v>375</v>
+      </c>
+      <c r="E97" s="8" t="s">
+        <v>381</v>
+      </c>
+      <c r="F97" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="G97" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="H97" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="I97" s="8" t="s">
+        <v>382</v>
+      </c>
+      <c r="J97" s="8">
+        <v>3.217511266E9</v>
+      </c>
+      <c r="K97" s="8" t="s">
+        <v>30</v>
+      </c>
+      <c r="L97" s="10" t="s">
+        <v>383</v>
+      </c>
+      <c r="M97" s="10" t="s">
+        <v>384</v>
+      </c>
       <c r="N97" s="1"/>
       <c r="O97" s="1"/>
       <c r="P97" s="1"/>
@@ -14379,18 +14634,42 @@
     </row>
     <row r="98" ht="14.25" customHeight="1">
       <c r="A98" s="1"/>
-      <c r="B98" s="1"/>
-      <c r="C98" s="1"/>
-      <c r="D98" s="1"/>
-      <c r="E98" s="1"/>
-      <c r="F98" s="1"/>
-      <c r="G98" s="1"/>
-      <c r="H98" s="1"/>
-      <c r="I98" s="1"/>
-      <c r="J98" s="1"/>
-      <c r="K98" s="1"/>
-      <c r="L98" s="1"/>
-      <c r="M98" s="1"/>
+      <c r="B98" s="8" t="s">
+        <v>385</v>
+      </c>
+      <c r="C98" s="8" t="s">
+        <v>334</v>
+      </c>
+      <c r="D98" s="8" t="s">
+        <v>334</v>
+      </c>
+      <c r="E98" s="8" t="s">
+        <v>336</v>
+      </c>
+      <c r="F98" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="G98" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="H98" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="I98" s="8" t="s">
+        <v>386</v>
+      </c>
+      <c r="J98" s="8">
+        <v>3.152775314E9</v>
+      </c>
+      <c r="K98" s="8" t="s">
+        <v>30</v>
+      </c>
+      <c r="L98" s="10" t="s">
+        <v>387</v>
+      </c>
+      <c r="M98" s="8" t="s">
+        <v>388</v>
+      </c>
       <c r="N98" s="1"/>
       <c r="O98" s="1"/>
       <c r="P98" s="1"/>
@@ -14405,18 +14684,42 @@
     </row>
     <row r="99" ht="14.25" customHeight="1">
       <c r="A99" s="1"/>
-      <c r="B99" s="1"/>
-      <c r="C99" s="1"/>
-      <c r="D99" s="1"/>
-      <c r="E99" s="1"/>
-      <c r="F99" s="1"/>
-      <c r="G99" s="1"/>
-      <c r="H99" s="1"/>
-      <c r="I99" s="1"/>
-      <c r="J99" s="1"/>
-      <c r="K99" s="1"/>
-      <c r="L99" s="1"/>
-      <c r="M99" s="1"/>
+      <c r="B99" s="8" t="s">
+        <v>389</v>
+      </c>
+      <c r="C99" s="8" t="s">
+        <v>374</v>
+      </c>
+      <c r="D99" s="8" t="s">
+        <v>375</v>
+      </c>
+      <c r="E99" s="8" t="s">
+        <v>390</v>
+      </c>
+      <c r="F99" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="G99" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="H99" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="I99" s="8" t="s">
+        <v>391</v>
+      </c>
+      <c r="J99" s="8">
+        <v>3.21749353E9</v>
+      </c>
+      <c r="K99" s="8" t="s">
+        <v>30</v>
+      </c>
+      <c r="L99" s="8" t="s">
+        <v>30</v>
+      </c>
+      <c r="M99" s="11" t="s">
+        <v>392</v>
+      </c>
       <c r="N99" s="1"/>
       <c r="O99" s="1"/>
       <c r="P99" s="1"/>
@@ -14431,18 +14734,42 @@
     </row>
     <row r="100" ht="14.25" customHeight="1">
       <c r="A100" s="1"/>
-      <c r="B100" s="1"/>
-      <c r="C100" s="1"/>
-      <c r="D100" s="1"/>
-      <c r="E100" s="1"/>
-      <c r="F100" s="1"/>
-      <c r="G100" s="1"/>
-      <c r="H100" s="1"/>
-      <c r="I100" s="1"/>
-      <c r="J100" s="1"/>
-      <c r="K100" s="1"/>
-      <c r="L100" s="1"/>
-      <c r="M100" s="1"/>
+      <c r="B100" s="8" t="s">
+        <v>393</v>
+      </c>
+      <c r="C100" s="8" t="s">
+        <v>374</v>
+      </c>
+      <c r="D100" s="8" t="s">
+        <v>375</v>
+      </c>
+      <c r="E100" s="8" t="s">
+        <v>394</v>
+      </c>
+      <c r="F100" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="G100" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="H100" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="I100" s="8" t="s">
+        <v>395</v>
+      </c>
+      <c r="J100" s="8">
+        <v>3.105255156E9</v>
+      </c>
+      <c r="K100" s="8" t="s">
+        <v>30</v>
+      </c>
+      <c r="L100" s="8" t="s">
+        <v>30</v>
+      </c>
+      <c r="M100" s="10" t="s">
+        <v>396</v>
+      </c>
       <c r="N100" s="1"/>
       <c r="O100" s="1"/>
       <c r="P100" s="1"/>
@@ -14457,18 +14784,42 @@
     </row>
     <row r="101" ht="14.25" customHeight="1">
       <c r="A101" s="1"/>
-      <c r="B101" s="1"/>
-      <c r="C101" s="1"/>
-      <c r="D101" s="1"/>
-      <c r="E101" s="1"/>
-      <c r="F101" s="1"/>
-      <c r="G101" s="1"/>
-      <c r="H101" s="1"/>
-      <c r="I101" s="1"/>
-      <c r="J101" s="1"/>
-      <c r="K101" s="1"/>
-      <c r="L101" s="1"/>
-      <c r="M101" s="1"/>
+      <c r="B101" s="8" t="s">
+        <v>397</v>
+      </c>
+      <c r="C101" s="8" t="s">
+        <v>304</v>
+      </c>
+      <c r="D101" s="8" t="s">
+        <v>304</v>
+      </c>
+      <c r="E101" s="8" t="s">
+        <v>304</v>
+      </c>
+      <c r="F101" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="G101" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="H101" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="I101" s="8" t="s">
+        <v>398</v>
+      </c>
+      <c r="J101" s="8">
+        <v>3.052047405E9</v>
+      </c>
+      <c r="K101" s="8">
+        <v>6.043221126E9</v>
+      </c>
+      <c r="L101" s="10" t="s">
+        <v>399</v>
+      </c>
+      <c r="M101" s="8" t="s">
+        <v>30</v>
+      </c>
       <c r="N101" s="1"/>
       <c r="O101" s="1"/>
       <c r="P101" s="1"/>
@@ -38777,12 +39128,23 @@
     <hyperlink r:id="rId24" ref="M90"/>
     <hyperlink r:id="rId25" ref="L91"/>
     <hyperlink r:id="rId26" ref="M91"/>
+    <hyperlink r:id="rId27" ref="M93"/>
+    <hyperlink r:id="rId28" ref="M94"/>
+    <hyperlink r:id="rId29" ref="M95"/>
+    <hyperlink r:id="rId30" ref="L96"/>
+    <hyperlink r:id="rId31" ref="M96"/>
+    <hyperlink r:id="rId32" ref="L97"/>
+    <hyperlink r:id="rId33" ref="M97"/>
+    <hyperlink r:id="rId34" ref="L98"/>
+    <hyperlink r:id="rId35" ref="M99"/>
+    <hyperlink r:id="rId36" ref="M100"/>
+    <hyperlink r:id="rId37" ref="L101"/>
   </hyperlinks>
   <printOptions/>
   <pageMargins bottom="0.75" footer="0.0" header="0.0" left="0.7" right="0.7" top="0.75"/>
   <pageSetup orientation="landscape"/>
-  <drawing r:id="rId27"/>
-  <legacyDrawing r:id="rId28"/>
+  <drawing r:id="rId38"/>
+  <legacyDrawing r:id="rId39"/>
 </worksheet>
 </file>
 
@@ -38807,10 +39169,10 @@
     <row r="2" ht="14.25" customHeight="1">
       <c r="A2" s="1"/>
       <c r="B2" s="1" t="s">
-        <v>358</v>
+        <v>400</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>359</v>
+        <v>401</v>
       </c>
       <c r="D2" s="1"/>
       <c r="E2" s="1"/>
@@ -38819,10 +39181,10 @@
     <row r="3" ht="14.25" customHeight="1">
       <c r="A3" s="1"/>
       <c r="B3" s="1" t="s">
-        <v>360</v>
+        <v>402</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>361</v>
+        <v>403</v>
       </c>
       <c r="D3" s="1"/>
       <c r="E3" s="1"/>
@@ -38831,10 +39193,10 @@
     <row r="4" ht="14.25" customHeight="1">
       <c r="A4" s="1"/>
       <c r="B4" s="1" t="s">
-        <v>360</v>
+        <v>402</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>362</v>
+        <v>404</v>
       </c>
       <c r="D4" s="1"/>
       <c r="E4" s="1"/>
